--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -24,25 +24,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>OrderNo</x:t>
+  </x:si>
+  <x:si>
     <x:t>Company</x:t>
   </x:si>
   <x:si>
     <x:t>Payment method</x:t>
   </x:si>
   <x:si>
-    <x:t>OrderNo</x:t>
+    <x:t>Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tax rate</x:t>
   </x:si>
   <x:si>
     <x:t>Ship date</x:t>
   </x:si>
   <x:si>
-    <x:t>Items total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tax rate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amount paid</x:t>
+    <x:t>{{item.Company}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PaymentMethod}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.OrderNo}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.TaxRate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Общий итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PaymentMethod}} Итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Company}} Итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Итог Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Итог Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum of Items total</x:t>
   </x:si>
   <x:si>
     <x:t>Sight Diver</x:t>
@@ -841,45 +880,6 @@
   </x:si>
   <x:si>
     <x:t>1860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.TaxRate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Итог Sum Amount paid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Итог Sum Items total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum Amount paid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum Items total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Company}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PaymentMethod}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.OrderNo}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PaymentMethod}} Итог</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Company}} Итог</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Общий итог</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum of Items total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2353,36 +2353,36 @@
   <x:sheetData>
     <x:row r="2" spans="1:8" ht="30.75" customHeight="1">
       <x:c r="B2" s="49" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="49" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="50" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="50" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F2" s="49" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="F2" s="49" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="50" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="50" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="20.1" customHeight="1">
       <x:c r="B3" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D3" s="51" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E3" s="52">
         <x:v>32266</x:v>
@@ -2399,13 +2399,13 @@
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="B4" s="48" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="51" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="52">
         <x:v>32251</x:v>
@@ -2422,13 +2422,13 @@
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="B5" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="51" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="52">
         <x:v>32163</x:v>
@@ -2445,13 +2445,13 @@
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="B6" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="51" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E6" s="52">
         <x:v>32454</x:v>
@@ -2468,13 +2468,13 @@
     </x:row>
     <x:row r="7" spans="1:8">
       <x:c r="B7" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="51" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="52">
         <x:v>32265</x:v>
@@ -2491,13 +2491,13 @@
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="B8" s="48" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="51" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="52">
         <x:v>32267</x:v>
@@ -2514,13 +2514,13 @@
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="B9" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="51" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="52">
         <x:v>32275</x:v>
@@ -2537,13 +2537,13 @@
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="B10" s="48" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" s="51" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E10" s="52">
         <x:v>32275</x:v>
@@ -2560,13 +2560,13 @@
     </x:row>
     <x:row r="11" spans="1:8">
       <x:c r="B11" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="51" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E11" s="52">
         <x:v>32282</x:v>
@@ -2583,13 +2583,13 @@
     </x:row>
     <x:row r="12" spans="1:8">
       <x:c r="B12" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="51" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E12" s="52">
         <x:v>32283</x:v>
@@ -2606,13 +2606,13 @@
     </x:row>
     <x:row r="13" spans="1:8">
       <x:c r="B13" s="48" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C13" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D13" s="51" t="s">
-        <x:v>32</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E13" s="52">
         <x:v>32289</x:v>
@@ -2629,13 +2629,13 @@
     </x:row>
     <x:row r="14" spans="1:8">
       <x:c r="B14" s="48" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D14" s="51" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="52">
         <x:v>32289</x:v>
@@ -2652,13 +2652,13 @@
     </x:row>
     <x:row r="15" spans="1:8">
       <x:c r="B15" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D15" s="51" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="52">
         <x:v>32289</x:v>
@@ -2675,13 +2675,13 @@
     </x:row>
     <x:row r="16" spans="1:8">
       <x:c r="B16" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D16" s="51" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E16" s="52">
         <x:v>32297</x:v>
@@ -2698,13 +2698,13 @@
     </x:row>
     <x:row r="17" spans="1:8">
       <x:c r="B17" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D17" s="51" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E17" s="52">
         <x:v>32307</x:v>
@@ -2721,13 +2721,13 @@
     </x:row>
     <x:row r="18" spans="1:8">
       <x:c r="B18" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D18" s="51" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E18" s="52">
         <x:v>32313</x:v>
@@ -2744,13 +2744,13 @@
     </x:row>
     <x:row r="19" spans="1:8">
       <x:c r="B19" s="48" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C19" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="51" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E19" s="52">
         <x:v>32319</x:v>
@@ -2767,13 +2767,13 @@
     </x:row>
     <x:row r="20" spans="1:8">
       <x:c r="B20" s="48" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="51" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="52">
         <x:v>32319</x:v>
@@ -2790,13 +2790,13 @@
     </x:row>
     <x:row r="21" spans="1:8">
       <x:c r="B21" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D21" s="51" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E21" s="52">
         <x:v>32319</x:v>
@@ -2813,13 +2813,13 @@
     </x:row>
     <x:row r="22" spans="1:8">
       <x:c r="B22" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D22" s="51" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="52">
         <x:v>32325</x:v>
@@ -2836,13 +2836,13 @@
     </x:row>
     <x:row r="23" spans="1:8">
       <x:c r="B23" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D23" s="51" t="s">
-        <x:v>52</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E23" s="52">
         <x:v>32326</x:v>
@@ -2859,13 +2859,13 @@
     </x:row>
     <x:row r="24" spans="1:8">
       <x:c r="B24" s="48" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D24" s="51" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E24" s="52">
         <x:v>32327</x:v>
@@ -2882,13 +2882,13 @@
     </x:row>
     <x:row r="25" spans="1:8">
       <x:c r="B25" s="48" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C25" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D25" s="51" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E25" s="52">
         <x:v>32328</x:v>
@@ -2905,13 +2905,13 @@
     </x:row>
     <x:row r="26" spans="1:8">
       <x:c r="B26" s="48" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D26" s="51" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E26" s="52">
         <x:v>32332</x:v>
@@ -2928,13 +2928,13 @@
     </x:row>
     <x:row r="27" spans="1:8">
       <x:c r="B27" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D27" s="51" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E27" s="52">
         <x:v>32332</x:v>
@@ -2951,13 +2951,13 @@
     </x:row>
     <x:row r="28" spans="1:8">
       <x:c r="B28" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C28" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D28" s="51" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E28" s="52">
         <x:v>32332</x:v>
@@ -2974,13 +2974,13 @@
     </x:row>
     <x:row r="29" spans="1:8">
       <x:c r="B29" s="48" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C29" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D29" s="51" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E29" s="52">
         <x:v>32343</x:v>
@@ -2997,13 +2997,13 @@
     </x:row>
     <x:row r="30" spans="1:8">
       <x:c r="B30" s="48" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C30" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D30" s="51" t="s">
-        <x:v>61</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E30" s="52">
         <x:v>32350</x:v>
@@ -3020,13 +3020,13 @@
     </x:row>
     <x:row r="31" spans="1:8">
       <x:c r="B31" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C31" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D31" s="51" t="s">
-        <x:v>62</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E31" s="52">
         <x:v>32356</x:v>
@@ -3043,13 +3043,13 @@
     </x:row>
     <x:row r="32" spans="1:8">
       <x:c r="B32" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C32" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D32" s="51" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E32" s="52">
         <x:v>32356</x:v>
@@ -3066,13 +3066,13 @@
     </x:row>
     <x:row r="33" spans="1:8">
       <x:c r="B33" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C33" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D33" s="51" t="s">
-        <x:v>65</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E33" s="52">
         <x:v>32357</x:v>
@@ -3089,13 +3089,13 @@
     </x:row>
     <x:row r="34" spans="1:8">
       <x:c r="B34" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D34" s="51" t="s">
-        <x:v>66</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E34" s="52">
         <x:v>32369</x:v>
@@ -3112,13 +3112,13 @@
     </x:row>
     <x:row r="35" spans="1:8">
       <x:c r="B35" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D35" s="51" t="s">
-        <x:v>67</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E35" s="52">
         <x:v>32372</x:v>
@@ -3135,13 +3135,13 @@
     </x:row>
     <x:row r="36" spans="1:8">
       <x:c r="B36" s="48" t="s">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C36" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D36" s="51" t="s">
-        <x:v>69</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E36" s="52">
         <x:v>32381</x:v>
@@ -3158,13 +3158,13 @@
     </x:row>
     <x:row r="37" spans="1:8">
       <x:c r="B37" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C37" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D37" s="51" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E37" s="52">
         <x:v>32382</x:v>
@@ -3181,13 +3181,13 @@
     </x:row>
     <x:row r="38" spans="1:8">
       <x:c r="B38" s="48" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C38" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D38" s="51" t="s">
-        <x:v>71</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E38" s="52">
         <x:v>32382</x:v>
@@ -3204,13 +3204,13 @@
     </x:row>
     <x:row r="39" spans="1:8">
       <x:c r="B39" s="48" t="s">
-        <x:v>72</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C39" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="51" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E39" s="52">
         <x:v>32387</x:v>
@@ -3227,13 +3227,13 @@
     </x:row>
     <x:row r="40" spans="1:8">
       <x:c r="B40" s="48" t="s">
-        <x:v>74</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C40" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D40" s="51" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E40" s="52">
         <x:v>32391</x:v>
@@ -3250,13 +3250,13 @@
     </x:row>
     <x:row r="41" spans="1:8">
       <x:c r="B41" s="48" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D41" s="51" t="s">
-        <x:v>77</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E41" s="52">
         <x:v>32403</x:v>
@@ -3273,13 +3273,13 @@
     </x:row>
     <x:row r="42" spans="1:8">
       <x:c r="B42" s="48" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C42" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D42" s="51" t="s">
-        <x:v>79</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E42" s="52">
         <x:v>32411</x:v>
@@ -3296,13 +3296,13 @@
     </x:row>
     <x:row r="43" spans="1:8">
       <x:c r="B43" s="48" t="s">
-        <x:v>80</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D43" s="51" t="s">
-        <x:v>81</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E43" s="52">
         <x:v>32417</x:v>
@@ -3319,13 +3319,13 @@
     </x:row>
     <x:row r="44" spans="1:8">
       <x:c r="B44" s="48" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C44" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D44" s="51" t="s">
-        <x:v>83</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E44" s="52">
         <x:v>32425</x:v>
@@ -3342,13 +3342,13 @@
     </x:row>
     <x:row r="45" spans="1:8">
       <x:c r="B45" s="48" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C45" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D45" s="51" t="s">
-        <x:v>85</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E45" s="52">
         <x:v>32433</x:v>
@@ -3365,13 +3365,13 @@
     </x:row>
     <x:row r="46" spans="1:8">
       <x:c r="B46" s="48" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C46" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D46" s="51" t="s">
-        <x:v>87</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E46" s="52">
         <x:v>32460</x:v>
@@ -3388,13 +3388,13 @@
     </x:row>
     <x:row r="47" spans="1:8">
       <x:c r="B47" s="48" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D47" s="51" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E47" s="52">
         <x:v>32475</x:v>
@@ -3411,13 +3411,13 @@
     </x:row>
     <x:row r="48" spans="1:8">
       <x:c r="B48" s="48" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C48" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D48" s="51" t="s">
-        <x:v>90</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E48" s="52">
         <x:v>32480</x:v>
@@ -3434,13 +3434,13 @@
     </x:row>
     <x:row r="49" spans="1:8">
       <x:c r="B49" s="48" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C49" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D49" s="51" t="s">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E49" s="52">
         <x:v>32491</x:v>
@@ -3457,13 +3457,13 @@
     </x:row>
     <x:row r="50" spans="1:8">
       <x:c r="B50" s="48" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C50" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D50" s="51" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E50" s="52">
         <x:v>32502</x:v>
@@ -3480,13 +3480,13 @@
     </x:row>
     <x:row r="51" spans="1:8">
       <x:c r="B51" s="48" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C51" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D51" s="51" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E51" s="52">
         <x:v>32513</x:v>
@@ -3503,13 +3503,13 @@
     </x:row>
     <x:row r="52" spans="1:8">
       <x:c r="B52" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C52" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D52" s="51" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E52" s="52">
         <x:v>32515</x:v>
@@ -3526,13 +3526,13 @@
     </x:row>
     <x:row r="53" spans="1:8">
       <x:c r="B53" s="48" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C53" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D53" s="51" t="s">
-        <x:v>98</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E53" s="52">
         <x:v>32524</x:v>
@@ -3549,13 +3549,13 @@
     </x:row>
     <x:row r="54" spans="1:8">
       <x:c r="B54" s="48" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C54" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D54" s="51" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E54" s="52">
         <x:v>32540</x:v>
@@ -3572,13 +3572,13 @@
     </x:row>
     <x:row r="55" spans="1:8">
       <x:c r="B55" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C55" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D55" s="51" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E55" s="52">
         <x:v>32544</x:v>
@@ -3595,13 +3595,13 @@
     </x:row>
     <x:row r="56" spans="1:8">
       <x:c r="B56" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C56" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D56" s="51" t="s">
-        <x:v>101</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E56" s="52">
         <x:v>32548</x:v>
@@ -3618,13 +3618,13 @@
     </x:row>
     <x:row r="57" spans="1:8">
       <x:c r="B57" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C57" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D57" s="51" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E57" s="52">
         <x:v>32558</x:v>
@@ -3641,13 +3641,13 @@
     </x:row>
     <x:row r="58" spans="1:8">
       <x:c r="B58" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C58" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D58" s="51" t="s">
-        <x:v>103</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E58" s="52">
         <x:v>32561</x:v>
@@ -3664,13 +3664,13 @@
     </x:row>
     <x:row r="59" spans="1:8">
       <x:c r="B59" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C59" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D59" s="51" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E59" s="52">
         <x:v>32564</x:v>
@@ -3687,13 +3687,13 @@
     </x:row>
     <x:row r="60" spans="1:8">
       <x:c r="B60" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C60" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D60" s="51" t="s">
-        <x:v>106</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E60" s="52">
         <x:v>32568</x:v>
@@ -3710,13 +3710,13 @@
     </x:row>
     <x:row r="61" spans="1:8">
       <x:c r="B61" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C61" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D61" s="51" t="s">
-        <x:v>107</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E61" s="52">
         <x:v>32571</x:v>
@@ -3733,13 +3733,13 @@
     </x:row>
     <x:row r="62" spans="1:8">
       <x:c r="B62" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C62" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D62" s="51" t="s">
-        <x:v>108</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E62" s="52">
         <x:v>32576</x:v>
@@ -3756,13 +3756,13 @@
     </x:row>
     <x:row r="63" spans="1:8">
       <x:c r="B63" s="48" t="s">
-        <x:v>109</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C63" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D63" s="51" t="s">
-        <x:v>110</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E63" s="52">
         <x:v>32581</x:v>
@@ -3779,13 +3779,13 @@
     </x:row>
     <x:row r="64" spans="1:8">
       <x:c r="B64" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C64" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D64" s="51" t="s">
-        <x:v>111</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E64" s="52">
         <x:v>32592</x:v>
@@ -3802,13 +3802,13 @@
     </x:row>
     <x:row r="65" spans="1:8">
       <x:c r="B65" s="48" t="s">
-        <x:v>112</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C65" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D65" s="51" t="s">
-        <x:v>113</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E65" s="52">
         <x:v>32593</x:v>
@@ -3825,13 +3825,13 @@
     </x:row>
     <x:row r="66" spans="1:8">
       <x:c r="B66" s="48" t="s">
-        <x:v>114</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C66" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D66" s="51" t="s">
-        <x:v>115</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E66" s="52">
         <x:v>32594</x:v>
@@ -3848,13 +3848,13 @@
     </x:row>
     <x:row r="67" spans="1:8">
       <x:c r="B67" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C67" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D67" s="51" t="s">
-        <x:v>116</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E67" s="52">
         <x:v>32600</x:v>
@@ -3871,13 +3871,13 @@
     </x:row>
     <x:row r="68" spans="1:8">
       <x:c r="B68" s="48" t="s">
-        <x:v>117</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C68" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D68" s="51" t="s">
-        <x:v>118</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E68" s="52">
         <x:v>32602</x:v>
@@ -3894,13 +3894,13 @@
     </x:row>
     <x:row r="69" spans="1:8">
       <x:c r="B69" s="48" t="s">
-        <x:v>119</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C69" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D69" s="51" t="s">
-        <x:v>120</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E69" s="52">
         <x:v>32604</x:v>
@@ -3917,13 +3917,13 @@
     </x:row>
     <x:row r="70" spans="1:8">
       <x:c r="B70" s="48" t="s">
-        <x:v>121</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C70" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D70" s="51" t="s">
-        <x:v>122</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E70" s="52">
         <x:v>32606</x:v>
@@ -3940,13 +3940,13 @@
     </x:row>
     <x:row r="71" spans="1:8">
       <x:c r="B71" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C71" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D71" s="51" t="s">
-        <x:v>123</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E71" s="52">
         <x:v>32608</x:v>
@@ -3963,13 +3963,13 @@
     </x:row>
     <x:row r="72" spans="1:8">
       <x:c r="B72" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C72" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D72" s="51" t="s">
-        <x:v>124</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E72" s="52">
         <x:v>32610</x:v>
@@ -3986,13 +3986,13 @@
     </x:row>
     <x:row r="73" spans="1:8">
       <x:c r="B73" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C73" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D73" s="51" t="s">
-        <x:v>125</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E73" s="52">
         <x:v>32614</x:v>
@@ -4009,13 +4009,13 @@
     </x:row>
     <x:row r="74" spans="1:8">
       <x:c r="B74" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C74" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D74" s="51" t="s">
-        <x:v>126</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E74" s="52">
         <x:v>32618</x:v>
@@ -4032,13 +4032,13 @@
     </x:row>
     <x:row r="75" spans="1:8">
       <x:c r="B75" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C75" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D75" s="51" t="s">
-        <x:v>127</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E75" s="52">
         <x:v>32620</x:v>
@@ -4055,13 +4055,13 @@
     </x:row>
     <x:row r="76" spans="1:8">
       <x:c r="B76" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C76" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D76" s="51" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E76" s="52">
         <x:v>32624</x:v>
@@ -4078,13 +4078,13 @@
     </x:row>
     <x:row r="77" spans="1:8">
       <x:c r="B77" s="48" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C77" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D77" s="51" t="s">
-        <x:v>129</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E77" s="52">
         <x:v>32629</x:v>
@@ -4101,13 +4101,13 @@
     </x:row>
     <x:row r="78" spans="1:8">
       <x:c r="B78" s="48" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C78" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D78" s="51" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E78" s="52">
         <x:v>32630</x:v>
@@ -4124,13 +4124,13 @@
     </x:row>
     <x:row r="79" spans="1:8">
       <x:c r="B79" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C79" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D79" s="51" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E79" s="52">
         <x:v>32632</x:v>
@@ -4147,13 +4147,13 @@
     </x:row>
     <x:row r="80" spans="1:8">
       <x:c r="B80" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D80" s="51" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E80" s="52">
         <x:v>32634</x:v>
@@ -4170,13 +4170,13 @@
     </x:row>
     <x:row r="81" spans="1:8">
       <x:c r="B81" s="48" t="s">
-        <x:v>109</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C81" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D81" s="51" t="s">
-        <x:v>134</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E81" s="52">
         <x:v>32636</x:v>
@@ -4193,13 +4193,13 @@
     </x:row>
     <x:row r="82" spans="1:8">
       <x:c r="B82" s="48" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C82" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D82" s="51" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E82" s="52">
         <x:v>32638</x:v>
@@ -4216,13 +4216,13 @@
     </x:row>
     <x:row r="83" spans="1:8">
       <x:c r="B83" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C83" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D83" s="51" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E83" s="52">
         <x:v>32638</x:v>
@@ -4239,13 +4239,13 @@
     </x:row>
     <x:row r="84" spans="1:8">
       <x:c r="B84" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C84" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D84" s="51" t="s">
-        <x:v>137</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E84" s="52">
         <x:v>32640</x:v>
@@ -4262,13 +4262,13 @@
     </x:row>
     <x:row r="85" spans="1:8">
       <x:c r="B85" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C85" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D85" s="51" t="s">
-        <x:v>138</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E85" s="52">
         <x:v>32647</x:v>
@@ -4285,13 +4285,13 @@
     </x:row>
     <x:row r="86" spans="1:8">
       <x:c r="B86" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C86" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D86" s="51" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E86" s="52">
         <x:v>32649</x:v>
@@ -4308,13 +4308,13 @@
     </x:row>
     <x:row r="87" spans="1:8">
       <x:c r="B87" s="48" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C87" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D87" s="51" t="s">
-        <x:v>140</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E87" s="52">
         <x:v>32651</x:v>
@@ -4331,13 +4331,13 @@
     </x:row>
     <x:row r="88" spans="1:8">
       <x:c r="B88" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C88" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D88" s="51" t="s">
-        <x:v>141</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E88" s="52">
         <x:v>32654</x:v>
@@ -4354,13 +4354,13 @@
     </x:row>
     <x:row r="89" spans="1:8">
       <x:c r="B89" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C89" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D89" s="51" t="s">
-        <x:v>142</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E89" s="52">
         <x:v>32660</x:v>
@@ -4377,13 +4377,13 @@
     </x:row>
     <x:row r="90" spans="1:8">
       <x:c r="B90" s="48" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C90" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D90" s="51" t="s">
-        <x:v>144</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E90" s="52">
         <x:v>32660</x:v>
@@ -4400,13 +4400,13 @@
     </x:row>
     <x:row r="91" spans="1:8">
       <x:c r="B91" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C91" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D91" s="51" t="s">
-        <x:v>145</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E91" s="52">
         <x:v>32661</x:v>
@@ -4423,13 +4423,13 @@
     </x:row>
     <x:row r="92" spans="1:8">
       <x:c r="B92" s="48" t="s">
-        <x:v>146</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C92" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D92" s="51" t="s">
-        <x:v>147</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E92" s="52">
         <x:v>32663</x:v>
@@ -4446,13 +4446,13 @@
     </x:row>
     <x:row r="93" spans="1:8">
       <x:c r="B93" s="48" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C93" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D93" s="51" t="s">
-        <x:v>148</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E93" s="52">
         <x:v>32665</x:v>
@@ -4469,13 +4469,13 @@
     </x:row>
     <x:row r="94" spans="1:8">
       <x:c r="B94" s="48" t="s">
-        <x:v>149</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C94" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D94" s="51" t="s">
-        <x:v>150</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E94" s="52">
         <x:v>32668</x:v>
@@ -4492,13 +4492,13 @@
     </x:row>
     <x:row r="95" spans="1:8">
       <x:c r="B95" s="48" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C95" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D95" s="51" t="s">
-        <x:v>151</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E95" s="52">
         <x:v>32671</x:v>
@@ -4515,13 +4515,13 @@
     </x:row>
     <x:row r="96" spans="1:8">
       <x:c r="B96" s="48" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C96" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D96" s="51" t="s">
-        <x:v>152</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E96" s="52">
         <x:v>32673</x:v>
@@ -4538,13 +4538,13 @@
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="B97" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C97" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D97" s="51" t="s">
-        <x:v>153</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E97" s="52">
         <x:v>32675</x:v>
@@ -4561,13 +4561,13 @@
     </x:row>
     <x:row r="98" spans="1:8">
       <x:c r="B98" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C98" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D98" s="51" t="s">
-        <x:v>154</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E98" s="52">
         <x:v>32679</x:v>
@@ -4584,13 +4584,13 @@
     </x:row>
     <x:row r="99" spans="1:8">
       <x:c r="B99" s="48" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C99" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D99" s="51" t="s">
-        <x:v>155</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E99" s="52">
         <x:v>32693</x:v>
@@ -4607,13 +4607,13 @@
     </x:row>
     <x:row r="100" spans="1:8">
       <x:c r="B100" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C100" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D100" s="51" t="s">
-        <x:v>156</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E100" s="52">
         <x:v>33761</x:v>
@@ -4630,13 +4630,13 @@
     </x:row>
     <x:row r="101" spans="1:8">
       <x:c r="B101" s="48" t="s">
-        <x:v>109</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C101" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D101" s="51" t="s">
-        <x:v>157</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E101" s="52">
         <x:v>33798</x:v>
@@ -4653,13 +4653,13 @@
     </x:row>
     <x:row r="102" spans="1:8">
       <x:c r="B102" s="48" t="s">
-        <x:v>158</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C102" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D102" s="51" t="s">
-        <x:v>159</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E102" s="52">
         <x:v>33803</x:v>
@@ -4676,13 +4676,13 @@
     </x:row>
     <x:row r="103" spans="1:8">
       <x:c r="B103" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C103" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D103" s="51" t="s">
-        <x:v>160</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E103" s="52">
         <x:v>33806</x:v>
@@ -4699,13 +4699,13 @@
     </x:row>
     <x:row r="104" spans="1:8">
       <x:c r="B104" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C104" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D104" s="51" t="s">
-        <x:v>161</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E104" s="52">
         <x:v>33870</x:v>
@@ -4722,13 +4722,13 @@
     </x:row>
     <x:row r="105" spans="1:8">
       <x:c r="B105" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C105" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D105" s="51" t="s">
-        <x:v>162</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E105" s="52">
         <x:v>33901</x:v>
@@ -4745,13 +4745,13 @@
     </x:row>
     <x:row r="106" spans="1:8">
       <x:c r="B106" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C106" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D106" s="51" t="s">
-        <x:v>163</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E106" s="52">
         <x:v>33921</x:v>
@@ -4768,13 +4768,13 @@
     </x:row>
     <x:row r="107" spans="1:8">
       <x:c r="B107" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C107" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D107" s="51" t="s">
-        <x:v>164</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E107" s="52">
         <x:v>33952</x:v>
@@ -4791,13 +4791,13 @@
     </x:row>
     <x:row r="108" spans="1:8">
       <x:c r="B108" s="48" t="s">
-        <x:v>117</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C108" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D108" s="51" t="s">
-        <x:v>165</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E108" s="52">
         <x:v>33971</x:v>
@@ -4814,13 +4814,13 @@
     </x:row>
     <x:row r="109" spans="1:8">
       <x:c r="B109" s="48" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C109" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D109" s="51" t="s">
-        <x:v>166</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E109" s="52">
         <x:v>34012</x:v>
@@ -4837,13 +4837,13 @@
     </x:row>
     <x:row r="110" spans="1:8">
       <x:c r="B110" s="48" t="s">
-        <x:v>167</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C110" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D110" s="51" t="s">
-        <x:v>168</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E110" s="52">
         <x:v>34041</x:v>
@@ -4860,13 +4860,13 @@
     </x:row>
     <x:row r="111" spans="1:8">
       <x:c r="B111" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C111" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D111" s="51" t="s">
-        <x:v>169</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E111" s="52">
         <x:v>34049</x:v>
@@ -4883,13 +4883,13 @@
     </x:row>
     <x:row r="112" spans="1:8">
       <x:c r="B112" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C112" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D112" s="51" t="s">
-        <x:v>170</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E112" s="52">
         <x:v>34072</x:v>
@@ -4906,13 +4906,13 @@
     </x:row>
     <x:row r="113" spans="1:8">
       <x:c r="B113" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C113" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D113" s="51" t="s">
-        <x:v>171</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E113" s="52">
         <x:v>34082</x:v>
@@ -4929,13 +4929,13 @@
     </x:row>
     <x:row r="114" spans="1:8">
       <x:c r="B114" s="48" t="s">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C114" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D114" s="51" t="s">
-        <x:v>172</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E114" s="52">
         <x:v>34104</x:v>
@@ -4952,13 +4952,13 @@
     </x:row>
     <x:row r="115" spans="1:8">
       <x:c r="B115" s="48" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C115" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D115" s="51" t="s">
-        <x:v>173</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E115" s="52">
         <x:v>34114</x:v>
@@ -4975,13 +4975,13 @@
     </x:row>
     <x:row r="116" spans="1:8">
       <x:c r="B116" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C116" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D116" s="51" t="s">
-        <x:v>174</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E116" s="52">
         <x:v>34122</x:v>
@@ -4998,13 +4998,13 @@
     </x:row>
     <x:row r="117" spans="1:8">
       <x:c r="B117" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C117" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D117" s="51" t="s">
-        <x:v>175</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E117" s="52">
         <x:v>34173</x:v>
@@ -5021,13 +5021,13 @@
     </x:row>
     <x:row r="118" spans="1:8">
       <x:c r="B118" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C118" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D118" s="51" t="s">
-        <x:v>176</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E118" s="52">
         <x:v>34205</x:v>
@@ -5044,13 +5044,13 @@
     </x:row>
     <x:row r="119" spans="1:8">
       <x:c r="B119" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C119" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D119" s="51" t="s">
-        <x:v>177</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E119" s="52">
         <x:v>34213</x:v>
@@ -5067,13 +5067,13 @@
     </x:row>
     <x:row r="120" spans="1:8">
       <x:c r="B120" s="48" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C120" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D120" s="51" t="s">
-        <x:v>178</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E120" s="52">
         <x:v>34216</x:v>
@@ -5090,13 +5090,13 @@
     </x:row>
     <x:row r="121" spans="1:8">
       <x:c r="B121" s="48" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C121" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D121" s="51" t="s">
-        <x:v>179</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E121" s="52">
         <x:v>34243</x:v>
@@ -5113,13 +5113,13 @@
     </x:row>
     <x:row r="122" spans="1:8">
       <x:c r="B122" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C122" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D122" s="51" t="s">
-        <x:v>180</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E122" s="52">
         <x:v>34244</x:v>
@@ -5136,13 +5136,13 @@
     </x:row>
     <x:row r="123" spans="1:8">
       <x:c r="B123" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C123" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D123" s="51" t="s">
-        <x:v>181</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E123" s="52">
         <x:v>34250</x:v>
@@ -5159,13 +5159,13 @@
     </x:row>
     <x:row r="124" spans="1:8">
       <x:c r="B124" s="48" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C124" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D124" s="51" t="s">
-        <x:v>182</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E124" s="52">
         <x:v>34261</x:v>
@@ -5182,13 +5182,13 @@
     </x:row>
     <x:row r="125" spans="1:8">
       <x:c r="B125" s="48" t="s">
-        <x:v>183</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C125" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D125" s="51" t="s">
-        <x:v>184</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E125" s="52">
         <x:v>34268</x:v>
@@ -5205,13 +5205,13 @@
     </x:row>
     <x:row r="126" spans="1:8">
       <x:c r="B126" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C126" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D126" s="51" t="s">
-        <x:v>185</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E126" s="52">
         <x:v>34274</x:v>
@@ -5228,13 +5228,13 @@
     </x:row>
     <x:row r="127" spans="1:8">
       <x:c r="B127" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C127" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D127" s="51" t="s">
-        <x:v>186</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E127" s="52">
         <x:v>34274</x:v>
@@ -5251,13 +5251,13 @@
     </x:row>
     <x:row r="128" spans="1:8">
       <x:c r="B128" s="48" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C128" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D128" s="51" t="s">
-        <x:v>187</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E128" s="52">
         <x:v>34275</x:v>
@@ -5274,13 +5274,13 @@
     </x:row>
     <x:row r="129" spans="1:8">
       <x:c r="B129" s="48" t="s">
-        <x:v>188</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C129" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D129" s="51" t="s">
-        <x:v>189</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E129" s="52">
         <x:v>34287</x:v>
@@ -5297,13 +5297,13 @@
     </x:row>
     <x:row r="130" spans="1:8">
       <x:c r="B130" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C130" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D130" s="51" t="s">
-        <x:v>190</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E130" s="52">
         <x:v>34300</x:v>
@@ -5320,13 +5320,13 @@
     </x:row>
     <x:row r="131" spans="1:8">
       <x:c r="B131" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C131" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D131" s="51" t="s">
-        <x:v>191</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E131" s="52">
         <x:v>34300</x:v>
@@ -5343,13 +5343,13 @@
     </x:row>
     <x:row r="132" spans="1:8">
       <x:c r="B132" s="48" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C132" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D132" s="51" t="s">
-        <x:v>192</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E132" s="52">
         <x:v>34304</x:v>
@@ -5366,13 +5366,13 @@
     </x:row>
     <x:row r="133" spans="1:8">
       <x:c r="B133" s="48" t="s">
-        <x:v>74</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C133" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D133" s="51" t="s">
-        <x:v>193</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E133" s="52">
         <x:v>34315</x:v>
@@ -5389,13 +5389,13 @@
     </x:row>
     <x:row r="134" spans="1:8">
       <x:c r="B134" s="48" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C134" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D134" s="51" t="s">
-        <x:v>194</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E134" s="52">
         <x:v>34320</x:v>
@@ -5412,13 +5412,13 @@
     </x:row>
     <x:row r="135" spans="1:8">
       <x:c r="B135" s="48" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C135" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D135" s="51" t="s">
-        <x:v>195</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E135" s="52">
         <x:v>34328</x:v>
@@ -5435,13 +5435,13 @@
     </x:row>
     <x:row r="136" spans="1:8">
       <x:c r="B136" s="48" t="s">
-        <x:v>80</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C136" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D136" s="51" t="s">
-        <x:v>196</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E136" s="52">
         <x:v>34335</x:v>
@@ -5458,13 +5458,13 @@
     </x:row>
     <x:row r="137" spans="1:8">
       <x:c r="B137" s="48" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C137" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="51" t="s">
-        <x:v>197</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E137" s="52">
         <x:v>34343</x:v>
@@ -5481,13 +5481,13 @@
     </x:row>
     <x:row r="138" spans="1:8">
       <x:c r="B138" s="48" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C138" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D138" s="51" t="s">
-        <x:v>198</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E138" s="52">
         <x:v>34351</x:v>
@@ -5504,13 +5504,13 @@
     </x:row>
     <x:row r="139" spans="1:8">
       <x:c r="B139" s="48" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C139" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D139" s="51" t="s">
-        <x:v>199</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E139" s="52">
         <x:v>34378</x:v>
@@ -5527,13 +5527,13 @@
     </x:row>
     <x:row r="140" spans="1:8">
       <x:c r="B140" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C140" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D140" s="51" t="s">
-        <x:v>200</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E140" s="52">
         <x:v>34396</x:v>
@@ -5550,13 +5550,13 @@
     </x:row>
     <x:row r="141" spans="1:8">
       <x:c r="B141" s="48" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C141" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D141" s="51" t="s">
-        <x:v>201</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E141" s="52">
         <x:v>34407</x:v>
@@ -5573,13 +5573,13 @@
     </x:row>
     <x:row r="142" spans="1:8">
       <x:c r="B142" s="48" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C142" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D142" s="51" t="s">
-        <x:v>202</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E142" s="52">
         <x:v>34418</x:v>
@@ -5596,13 +5596,13 @@
     </x:row>
     <x:row r="143" spans="1:8">
       <x:c r="B143" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C143" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D143" s="51" t="s">
-        <x:v>203</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E143" s="52">
         <x:v>34431</x:v>
@@ -5619,13 +5619,13 @@
     </x:row>
     <x:row r="144" spans="1:8">
       <x:c r="B144" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C144" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D144" s="51" t="s">
-        <x:v>204</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E144" s="52">
         <x:v>34440</x:v>
@@ -5642,13 +5642,13 @@
     </x:row>
     <x:row r="145" spans="1:8">
       <x:c r="B145" s="48" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C145" s="51" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C145" s="51" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="D145" s="51" t="s">
-        <x:v>205</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E145" s="52">
         <x:v>34455</x:v>
@@ -5665,13 +5665,13 @@
     </x:row>
     <x:row r="146" spans="1:8">
       <x:c r="B146" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C146" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D146" s="51" t="s">
-        <x:v>206</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E146" s="52">
         <x:v>34459</x:v>
@@ -5688,13 +5688,13 @@
     </x:row>
     <x:row r="147" spans="1:8">
       <x:c r="B147" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C147" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D147" s="51" t="s">
-        <x:v>207</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E147" s="52">
         <x:v>34463</x:v>
@@ -5711,13 +5711,13 @@
     </x:row>
     <x:row r="148" spans="1:8">
       <x:c r="B148" s="48" t="s">
-        <x:v>208</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C148" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D148" s="51" t="s">
-        <x:v>209</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E148" s="52">
         <x:v>34476</x:v>
@@ -5734,13 +5734,13 @@
     </x:row>
     <x:row r="149" spans="1:8">
       <x:c r="B149" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C149" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D149" s="51" t="s">
-        <x:v>210</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E149" s="52">
         <x:v>34486</x:v>
@@ -5757,13 +5757,13 @@
     </x:row>
     <x:row r="150" spans="1:8">
       <x:c r="B150" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C150" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D150" s="51" t="s">
-        <x:v>211</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E150" s="52">
         <x:v>34489</x:v>
@@ -5780,13 +5780,13 @@
     </x:row>
     <x:row r="151" spans="1:8">
       <x:c r="B151" s="48" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C151" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D151" s="51" t="s">
-        <x:v>212</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E151" s="52">
         <x:v>34494</x:v>
@@ -5803,13 +5803,13 @@
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="B152" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C152" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D152" s="51" t="s">
-        <x:v>213</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E152" s="52">
         <x:v>34499</x:v>
@@ -5826,13 +5826,13 @@
     </x:row>
     <x:row r="153" spans="1:8">
       <x:c r="B153" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C153" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D153" s="51" t="s">
-        <x:v>214</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E153" s="52">
         <x:v>34511</x:v>
@@ -5849,13 +5849,13 @@
     </x:row>
     <x:row r="154" spans="1:8">
       <x:c r="B154" s="48" t="s">
-        <x:v>114</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C154" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D154" s="51" t="s">
-        <x:v>215</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E154" s="52">
         <x:v>34516</x:v>
@@ -5872,13 +5872,13 @@
     </x:row>
     <x:row r="155" spans="1:8">
       <x:c r="B155" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C155" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D155" s="51" t="s">
-        <x:v>216</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E155" s="52">
         <x:v>34519</x:v>
@@ -5895,13 +5895,13 @@
     </x:row>
     <x:row r="156" spans="1:8">
       <x:c r="B156" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C156" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D156" s="51" t="s">
-        <x:v>217</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E156" s="52">
         <x:v>34521</x:v>
@@ -5918,13 +5918,13 @@
     </x:row>
     <x:row r="157" spans="1:8">
       <x:c r="B157" s="48" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C157" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D157" s="51" t="s">
-        <x:v>218</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E157" s="52">
         <x:v>34523</x:v>
@@ -5941,13 +5941,13 @@
     </x:row>
     <x:row r="158" spans="1:8">
       <x:c r="B158" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C158" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D158" s="51" t="s">
-        <x:v>219</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E158" s="52">
         <x:v>34525</x:v>
@@ -5964,13 +5964,13 @@
     </x:row>
     <x:row r="159" spans="1:8">
       <x:c r="B159" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C159" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D159" s="51" t="s">
-        <x:v>220</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E159" s="52">
         <x:v>34531</x:v>
@@ -5987,13 +5987,13 @@
     </x:row>
     <x:row r="160" spans="1:8">
       <x:c r="B160" s="48" t="s">
-        <x:v>221</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C160" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D160" s="51" t="s">
-        <x:v>222</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E160" s="52">
         <x:v>34537</x:v>
@@ -6010,13 +6010,13 @@
     </x:row>
     <x:row r="161" spans="1:8">
       <x:c r="B161" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C161" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D161" s="51" t="s">
-        <x:v>223</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E161" s="52">
         <x:v>34541</x:v>
@@ -6033,13 +6033,13 @@
     </x:row>
     <x:row r="162" spans="1:8">
       <x:c r="B162" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C162" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D162" s="51" t="s">
-        <x:v>224</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E162" s="52">
         <x:v>34548</x:v>
@@ -6056,13 +6056,13 @@
     </x:row>
     <x:row r="163" spans="1:8">
       <x:c r="B163" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C163" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D163" s="51" t="s">
-        <x:v>225</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E163" s="52">
         <x:v>34552</x:v>
@@ -6079,13 +6079,13 @@
     </x:row>
     <x:row r="164" spans="1:8">
       <x:c r="B164" s="48" t="s">
-        <x:v>117</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C164" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D164" s="51" t="s">
-        <x:v>226</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E164" s="52">
         <x:v>34556</x:v>
@@ -6102,13 +6102,13 @@
     </x:row>
     <x:row r="165" spans="1:8">
       <x:c r="B165" s="48" t="s">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C165" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D165" s="51" t="s">
-        <x:v>227</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E165" s="52">
         <x:v>34583</x:v>
@@ -6125,13 +6125,13 @@
     </x:row>
     <x:row r="166" spans="1:8">
       <x:c r="B166" s="48" t="s">
-        <x:v>149</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C166" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D166" s="51" t="s">
-        <x:v>228</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E166" s="52">
         <x:v>34585</x:v>
@@ -6148,13 +6148,13 @@
     </x:row>
     <x:row r="167" spans="1:8">
       <x:c r="B167" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C167" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D167" s="51" t="s">
-        <x:v>229</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E167" s="52">
         <x:v>34589</x:v>
@@ -6171,13 +6171,13 @@
     </x:row>
     <x:row r="168" spans="1:8">
       <x:c r="B168" s="48" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C168" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D168" s="51" t="s">
-        <x:v>230</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E168" s="52">
         <x:v>34591</x:v>
@@ -6194,13 +6194,13 @@
     </x:row>
     <x:row r="169" spans="1:8">
       <x:c r="B169" s="48" t="s">
-        <x:v>146</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C169" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D169" s="51" t="s">
-        <x:v>231</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E169" s="52">
         <x:v>34593</x:v>
@@ -6217,13 +6217,13 @@
     </x:row>
     <x:row r="170" spans="1:8">
       <x:c r="B170" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C170" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D170" s="51" t="s">
-        <x:v>232</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E170" s="52">
         <x:v>34597</x:v>
@@ -6240,13 +6240,13 @@
     </x:row>
     <x:row r="171" spans="1:8">
       <x:c r="B171" s="48" t="s">
-        <x:v>233</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C171" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D171" s="51" t="s">
-        <x:v>234</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E171" s="52">
         <x:v>34611</x:v>
@@ -6263,13 +6263,13 @@
     </x:row>
     <x:row r="172" spans="1:8">
       <x:c r="B172" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C172" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D172" s="51" t="s">
-        <x:v>235</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E172" s="52">
         <x:v>34613</x:v>
@@ -6286,13 +6286,13 @@
     </x:row>
     <x:row r="173" spans="1:8">
       <x:c r="B173" s="48" t="s">
-        <x:v>236</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C173" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D173" s="51" t="s">
-        <x:v>237</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E173" s="52">
         <x:v>34625</x:v>
@@ -6309,13 +6309,13 @@
     </x:row>
     <x:row r="174" spans="1:8">
       <x:c r="B174" s="48" t="s">
-        <x:v>114</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C174" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D174" s="51" t="s">
-        <x:v>238</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E174" s="52">
         <x:v>34628</x:v>
@@ -6332,13 +6332,13 @@
     </x:row>
     <x:row r="175" spans="1:8">
       <x:c r="B175" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C175" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D175" s="51" t="s">
-        <x:v>239</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E175" s="52">
         <x:v>34649</x:v>
@@ -6355,13 +6355,13 @@
     </x:row>
     <x:row r="176" spans="1:8">
       <x:c r="B176" s="48" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C176" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D176" s="51" t="s">
-        <x:v>240</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E176" s="52">
         <x:v>34650</x:v>
@@ -6378,13 +6378,13 @@
     </x:row>
     <x:row r="177" spans="1:8">
       <x:c r="B177" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C177" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D177" s="51" t="s">
-        <x:v>241</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E177" s="52">
         <x:v>34652</x:v>
@@ -6401,13 +6401,13 @@
     </x:row>
     <x:row r="178" spans="1:8">
       <x:c r="B178" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C178" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D178" s="51" t="s">
-        <x:v>242</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E178" s="52">
         <x:v>34654</x:v>
@@ -6424,13 +6424,13 @@
     </x:row>
     <x:row r="179" spans="1:8">
       <x:c r="B179" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C179" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D179" s="51" t="s">
-        <x:v>243</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E179" s="52">
         <x:v>34660</x:v>
@@ -6447,13 +6447,13 @@
     </x:row>
     <x:row r="180" spans="1:8">
       <x:c r="B180" s="48" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C180" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D180" s="51" t="s">
-        <x:v>244</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E180" s="52">
         <x:v>34661</x:v>
@@ -6470,13 +6470,13 @@
     </x:row>
     <x:row r="181" spans="1:8">
       <x:c r="B181" s="48" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C181" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D181" s="51" t="s">
-        <x:v>245</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E181" s="52">
         <x:v>34662</x:v>
@@ -6493,13 +6493,13 @@
     </x:row>
     <x:row r="182" spans="1:8">
       <x:c r="B182" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C182" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D182" s="51" t="s">
-        <x:v>246</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E182" s="52">
         <x:v>34664</x:v>
@@ -6516,13 +6516,13 @@
     </x:row>
     <x:row r="183" spans="1:8">
       <x:c r="B183" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C183" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D183" s="51" t="s">
-        <x:v>247</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E183" s="52">
         <x:v>34677</x:v>
@@ -6539,13 +6539,13 @@
     </x:row>
     <x:row r="184" spans="1:8">
       <x:c r="B184" s="48" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C184" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D184" s="51" t="s">
-        <x:v>248</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E184" s="52">
         <x:v>34678</x:v>
@@ -6562,13 +6562,13 @@
     </x:row>
     <x:row r="185" spans="1:8">
       <x:c r="B185" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C185" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D185" s="51" t="s">
-        <x:v>249</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E185" s="52">
         <x:v>34679</x:v>
@@ -6585,13 +6585,13 @@
     </x:row>
     <x:row r="186" spans="1:8">
       <x:c r="B186" s="48" t="s">
-        <x:v>236</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C186" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D186" s="51" t="s">
-        <x:v>250</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E186" s="52">
         <x:v>34682</x:v>
@@ -6608,13 +6608,13 @@
     </x:row>
     <x:row r="187" spans="1:8">
       <x:c r="B187" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C187" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D187" s="51" t="s">
-        <x:v>251</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E187" s="52">
         <x:v>34683</x:v>
@@ -6631,13 +6631,13 @@
     </x:row>
     <x:row r="188" spans="1:8">
       <x:c r="B188" s="48" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C188" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D188" s="51" t="s">
-        <x:v>252</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E188" s="52">
         <x:v>34684</x:v>
@@ -6654,13 +6654,13 @@
     </x:row>
     <x:row r="189" spans="1:8">
       <x:c r="B189" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C189" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D189" s="51" t="s">
-        <x:v>253</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E189" s="52">
         <x:v>34688</x:v>
@@ -6677,13 +6677,13 @@
     </x:row>
     <x:row r="190" spans="1:8">
       <x:c r="B190" s="48" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C190" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D190" s="51" t="s">
-        <x:v>254</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E190" s="52">
         <x:v>34690</x:v>
@@ -6700,13 +6700,13 @@
     </x:row>
     <x:row r="191" spans="1:8">
       <x:c r="B191" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C191" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D191" s="51" t="s">
-        <x:v>255</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E191" s="52">
         <x:v>34691</x:v>
@@ -6723,13 +6723,13 @@
     </x:row>
     <x:row r="192" spans="1:8">
       <x:c r="B192" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C192" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D192" s="51" t="s">
-        <x:v>256</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E192" s="52">
         <x:v>34694</x:v>
@@ -6746,13 +6746,13 @@
     </x:row>
     <x:row r="193" spans="1:8">
       <x:c r="B193" s="48" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C193" s="51" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D193" s="51" t="s">
-        <x:v>257</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E193" s="52">
         <x:v>34698</x:v>
@@ -6769,13 +6769,13 @@
     </x:row>
     <x:row r="194" spans="1:8">
       <x:c r="B194" s="48" t="s">
-        <x:v>158</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C194" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D194" s="51" t="s">
-        <x:v>258</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E194" s="52">
         <x:v>34700</x:v>
@@ -6792,13 +6792,13 @@
     </x:row>
     <x:row r="195" spans="1:8">
       <x:c r="B195" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C195" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D195" s="51" t="s">
-        <x:v>259</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E195" s="52">
         <x:v>34703</x:v>
@@ -6815,13 +6815,13 @@
     </x:row>
     <x:row r="196" spans="1:8">
       <x:c r="B196" s="48" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C196" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D196" s="51" t="s">
-        <x:v>260</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E196" s="52">
         <x:v>34705</x:v>
@@ -6838,13 +6838,13 @@
     </x:row>
     <x:row r="197" spans="1:8">
       <x:c r="B197" s="48" t="s">
-        <x:v>261</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C197" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D197" s="51" t="s">
-        <x:v>262</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E197" s="52">
         <x:v>34707</x:v>
@@ -6861,13 +6861,13 @@
     </x:row>
     <x:row r="198" spans="1:8">
       <x:c r="B198" s="48" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C198" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D198" s="51" t="s">
-        <x:v>263</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E198" s="52">
         <x:v>34708</x:v>
@@ -6884,13 +6884,13 @@
     </x:row>
     <x:row r="199" spans="1:8">
       <x:c r="B199" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C199" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D199" s="51" t="s">
-        <x:v>264</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E199" s="52">
         <x:v>34709</x:v>
@@ -6907,13 +6907,13 @@
     </x:row>
     <x:row r="200" spans="1:8">
       <x:c r="B200" s="48" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C200" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D200" s="51" t="s">
-        <x:v>265</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E200" s="52">
         <x:v>34715</x:v>
@@ -6930,13 +6930,13 @@
     </x:row>
     <x:row r="201" spans="1:8">
       <x:c r="B201" s="48" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C201" s="51" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D201" s="51" t="s">
-        <x:v>266</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E201" s="52">
         <x:v>34719</x:v>
@@ -6953,13 +6953,13 @@
     </x:row>
     <x:row r="202" spans="1:8">
       <x:c r="B202" s="48" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C202" s="51" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D202" s="51" t="s">
-        <x:v>267</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E202" s="52">
         <x:v>34721</x:v>
@@ -6976,13 +6976,13 @@
     </x:row>
     <x:row r="203" spans="1:8">
       <x:c r="B203" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C203" s="51" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D203" s="51" t="s">
-        <x:v>268</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E203" s="52">
         <x:v>34725</x:v>
@@ -6999,13 +6999,13 @@
     </x:row>
     <x:row r="204" spans="1:8">
       <x:c r="B204" s="48" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C204" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D204" s="51" t="s">
-        <x:v>269</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="E204" s="52">
         <x:v>34731</x:v>
@@ -7022,13 +7022,13 @@
     </x:row>
     <x:row r="205" spans="1:8">
       <x:c r="B205" s="48" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C205" s="51" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D205" s="51" t="s">
-        <x:v>270</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E205" s="52">
         <x:v>34732</x:v>
@@ -7045,13 +7045,13 @@
     </x:row>
     <x:row r="206" spans="1:8">
       <x:c r="B206" s="48" t="s">
-        <x:v>236</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C206" s="51" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D206" s="51" t="s">
-        <x:v>271</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E206" s="52">
         <x:v>34735</x:v>
@@ -7068,13 +7068,13 @@
     </x:row>
     <x:row r="207" spans="1:8">
       <x:c r="B207" s="48" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C207" s="51" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D207" s="51" t="s">
-        <x:v>272</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E207" s="52"/>
       <x:c r="F207" s="53">
@@ -7126,7 +7126,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>273</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="6"/>
       <x:c r="H3" s="7"/>
@@ -7136,44 +7136,44 @@
       <x:c r="C4" s="8"/>
       <x:c r="D4" s="8"/>
       <x:c r="E4" s="11" t="s">
-        <x:v>274</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="6"/>
       <x:c r="G4" s="11" t="s">
-        <x:v>275</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H4" s="40" t="s">
-        <x:v>276</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8" ht="25.5" customHeight="1">
       <x:c r="B5" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="13" t="s">
-        <x:v>277</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="13" t="s">
-        <x:v>278</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G5" s="9"/>
       <x:c r="H5" s="41"/>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="B6" s="3" t="s">
-        <x:v>279</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>280</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>281</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="3">
         <x:v>0</x:v>
@@ -7191,7 +7191,7 @@
     <x:row r="7" spans="1:8">
       <x:c r="B7" s="3"/>
       <x:c r="C7" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3">
@@ -7209,7 +7209,7 @@
     </x:row>
     <x:row r="8" spans="1:8" ht="12" customHeight="1">
       <x:c r="B8" s="3" t="s">
-        <x:v>283</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="3"/>
@@ -7228,7 +7228,7 @@
     </x:row>
     <x:row r="9" spans="1:8" ht="12.75" customHeight="1">
       <x:c r="B9" s="3" t="s">
-        <x:v>284</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="3"/>
       <x:c r="D9" s="3"/>
@@ -7281,34 +7281,34 @@
   <x:sheetData>
     <x:row r="4" spans="1:5">
       <x:c r="B4" s="4" t="s">
-        <x:v>285</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="6"/>
       <x:c r="D4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="B5" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>280</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>284</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="B6" s="11" t="s">
-        <x:v>279</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>281</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="11">
         <x:v>0</x:v>
@@ -7319,7 +7319,7 @@
     </x:row>
     <x:row r="7" spans="1:5" ht="11.25" customHeight="1">
       <x:c r="B7" s="11" t="s">
-        <x:v>283</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11">
@@ -7331,7 +7331,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="B8" s="11" t="s">
-        <x:v>284</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11">

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -2350,4744 +2350,4747 @@
     <x:col min="1" max="1" width="5.164062" style="0" customWidth="1"/>
     <x:col min="2" max="8" width="10.832031" style="0" customWidth="1"/>
   </x:cols>
-  <x:sheetData>
-    <x:row r="2" spans="1:8" ht="30.75" customHeight="1">
-      <x:c r="B2" s="49" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="49" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="50" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2" s="50" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F2" s="49" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G2" s="50" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H2" s="50" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="20.1" customHeight="1">
-      <x:c r="B3" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C3" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="51" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="52">
-        <x:v>32266</x:v>
-      </x:c>
-      <x:c r="F3" s="53">
-        <x:v>1250</x:v>
-      </x:c>
-      <x:c r="G3" s="54">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="H3" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="B4" s="48" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D4" s="51" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E4" s="52">
-        <x:v>32251</x:v>
-      </x:c>
-      <x:c r="F4" s="53">
-        <x:v>7885</x:v>
-      </x:c>
-      <x:c r="G4" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="53">
-        <x:v>7885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
-      <x:c r="B5" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C5" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="51" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E5" s="52">
-        <x:v>32163</x:v>
-      </x:c>
-      <x:c r="F5" s="53">
-        <x:v>4807</x:v>
-      </x:c>
-      <x:c r="G5" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="53">
-        <x:v>4807</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="B6" s="48" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="51" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E6" s="52">
-        <x:v>32454</x:v>
-      </x:c>
-      <x:c r="F6" s="53">
-        <x:v>31987</x:v>
-      </x:c>
-      <x:c r="G6" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="B7" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C7" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="51" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E7" s="52">
-        <x:v>32265</x:v>
-      </x:c>
-      <x:c r="F7" s="53">
-        <x:v>6500</x:v>
-      </x:c>
-      <x:c r="G7" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="53">
-        <x:v>6500</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
-      <x:c r="B8" s="48" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="51" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E8" s="52">
-        <x:v>32267</x:v>
-      </x:c>
-      <x:c r="F8" s="53">
-        <x:v>1449.5</x:v>
-      </x:c>
-      <x:c r="G8" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
-      <x:c r="B9" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D9" s="51" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E9" s="52">
-        <x:v>32275</x:v>
-      </x:c>
-      <x:c r="F9" s="53">
-        <x:v>5587</x:v>
-      </x:c>
-      <x:c r="G9" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
-      <x:c r="B10" s="48" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C10" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D10" s="51" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E10" s="52">
-        <x:v>32275</x:v>
-      </x:c>
-      <x:c r="F10" s="53">
-        <x:v>4996</x:v>
-      </x:c>
-      <x:c r="G10" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="53">
-        <x:v>4996</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
-      <x:c r="B11" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C11" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="51" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E11" s="52">
-        <x:v>32282</x:v>
-      </x:c>
-      <x:c r="F11" s="53">
-        <x:v>2679.85</x:v>
-      </x:c>
-      <x:c r="G11" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="53">
-        <x:v>2679.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
-      <x:c r="B12" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C12" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D12" s="51" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E12" s="52">
-        <x:v>32283</x:v>
-      </x:c>
-      <x:c r="F12" s="53">
-        <x:v>5201</x:v>
-      </x:c>
-      <x:c r="G12" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="53">
-        <x:v>5201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8">
-      <x:c r="B13" s="48" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C13" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D13" s="51" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E13" s="52">
-        <x:v>32289</x:v>
-      </x:c>
-      <x:c r="F13" s="53">
-        <x:v>3115</x:v>
-      </x:c>
-      <x:c r="G13" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="53">
-        <x:v>3115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8">
-      <x:c r="B14" s="48" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C14" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D14" s="51" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E14" s="52">
-        <x:v>32289</x:v>
-      </x:c>
-      <x:c r="F14" s="53">
-        <x:v>134.85</x:v>
-      </x:c>
-      <x:c r="G14" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="53">
-        <x:v>134.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:8">
-      <x:c r="B15" s="48" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C15" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D15" s="51" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E15" s="52">
-        <x:v>32289</x:v>
-      </x:c>
-      <x:c r="F15" s="53">
-        <x:v>20321.75</x:v>
-      </x:c>
-      <x:c r="G15" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="53">
-        <x:v>20321.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:8">
-      <x:c r="B16" s="48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D16" s="51" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E16" s="52">
-        <x:v>32297</x:v>
-      </x:c>
-      <x:c r="F16" s="53">
-        <x:v>2605</x:v>
-      </x:c>
-      <x:c r="G16" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8">
-      <x:c r="B17" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C17" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D17" s="51" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E17" s="52">
-        <x:v>32307</x:v>
-      </x:c>
-      <x:c r="F17" s="53">
-        <x:v>10195</x:v>
-      </x:c>
-      <x:c r="G17" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:8">
-      <x:c r="B18" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C18" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D18" s="51" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E18" s="52">
-        <x:v>32313</x:v>
-      </x:c>
-      <x:c r="F18" s="53">
-        <x:v>5256</x:v>
-      </x:c>
-      <x:c r="G18" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:8">
-      <x:c r="B19" s="48" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C19" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D19" s="51" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E19" s="52">
-        <x:v>32319</x:v>
-      </x:c>
-      <x:c r="F19" s="53">
-        <x:v>20602</x:v>
-      </x:c>
-      <x:c r="G19" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:8">
-      <x:c r="B20" s="48" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C20" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D20" s="51" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E20" s="52">
-        <x:v>32319</x:v>
-      </x:c>
-      <x:c r="F20" s="53">
-        <x:v>9955</x:v>
-      </x:c>
-      <x:c r="G20" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="53">
-        <x:v>9955</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:8">
-      <x:c r="B21" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C21" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D21" s="51" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E21" s="52">
-        <x:v>32319</x:v>
-      </x:c>
-      <x:c r="F21" s="53">
-        <x:v>3719</x:v>
-      </x:c>
-      <x:c r="G21" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="53">
-        <x:v>3719</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:8">
-      <x:c r="B22" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C22" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D22" s="51" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E22" s="52">
-        <x:v>32325</x:v>
-      </x:c>
-      <x:c r="F22" s="53">
-        <x:v>10064.65</x:v>
-      </x:c>
-      <x:c r="G22" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="53">
-        <x:v>10064.65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:8">
-      <x:c r="B23" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C23" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D23" s="51" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E23" s="52">
-        <x:v>32326</x:v>
-      </x:c>
-      <x:c r="F23" s="53">
-        <x:v>4674</x:v>
-      </x:c>
-      <x:c r="G23" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="53">
-        <x:v>4674</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:8">
-      <x:c r="B24" s="48" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C24" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D24" s="51" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E24" s="52">
-        <x:v>32327</x:v>
-      </x:c>
-      <x:c r="F24" s="53">
-        <x:v>6897</x:v>
-      </x:c>
-      <x:c r="G24" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="53">
-        <x:v>6897</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:8">
-      <x:c r="B25" s="48" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C25" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D25" s="51" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E25" s="52">
-        <x:v>32328</x:v>
-      </x:c>
-      <x:c r="F25" s="53">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="G25" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="53">
-        <x:v>930</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:8">
-      <x:c r="B26" s="48" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C26" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D26" s="51" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E26" s="52">
-        <x:v>32332</x:v>
-      </x:c>
-      <x:c r="F26" s="53">
-        <x:v>2920</x:v>
-      </x:c>
-      <x:c r="G26" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="53">
-        <x:v>2920</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:8">
-      <x:c r="B27" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C27" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D27" s="51" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E27" s="52">
-        <x:v>32332</x:v>
-      </x:c>
-      <x:c r="F27" s="53">
-        <x:v>25210</x:v>
-      </x:c>
-      <x:c r="G27" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="53">
-        <x:v>25210</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:8">
-      <x:c r="B28" s="48" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C28" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D28" s="51" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E28" s="52">
-        <x:v>32332</x:v>
-      </x:c>
-      <x:c r="F28" s="53">
-        <x:v>343.8</x:v>
-      </x:c>
-      <x:c r="G28" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="53">
-        <x:v>343.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:8">
-      <x:c r="B29" s="48" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C29" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D29" s="51" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E29" s="52">
-        <x:v>32343</x:v>
-      </x:c>
-      <x:c r="F29" s="53">
-        <x:v>20108</x:v>
-      </x:c>
-      <x:c r="G29" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="53">
-        <x:v>20108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:8">
-      <x:c r="B30" s="48" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C30" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D30" s="51" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E30" s="52">
-        <x:v>32350</x:v>
-      </x:c>
-      <x:c r="F30" s="53">
-        <x:v>559.6</x:v>
-      </x:c>
-      <x:c r="G30" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="53">
-        <x:v>559.6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:8">
-      <x:c r="B31" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C31" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D31" s="51" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E31" s="52">
-        <x:v>32356</x:v>
-      </x:c>
-      <x:c r="F31" s="53">
-        <x:v>12685</x:v>
-      </x:c>
-      <x:c r="G31" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H31" s="53">
-        <x:v>12685</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:8">
-      <x:c r="B32" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C32" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D32" s="51" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E32" s="52">
-        <x:v>32356</x:v>
-      </x:c>
-      <x:c r="F32" s="53">
-        <x:v>775</x:v>
-      </x:c>
-      <x:c r="G32" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="53">
-        <x:v>775</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:8">
-      <x:c r="B33" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C33" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D33" s="51" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E33" s="52">
-        <x:v>32357</x:v>
-      </x:c>
-      <x:c r="F33" s="53">
-        <x:v>1238</x:v>
-      </x:c>
-      <x:c r="G33" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="53">
-        <x:v>1238</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:8">
-      <x:c r="B34" s="48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C34" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D34" s="51" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E34" s="52">
-        <x:v>32369</x:v>
-      </x:c>
-      <x:c r="F34" s="53">
-        <x:v>18532</x:v>
-      </x:c>
-      <x:c r="G34" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="53">
-        <x:v>18532</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:8">
-      <x:c r="B35" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C35" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D35" s="51" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E35" s="52">
-        <x:v>32372</x:v>
-      </x:c>
-      <x:c r="F35" s="53">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="G35" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="53">
-        <x:v>560</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:8">
-      <x:c r="B36" s="48" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C36" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D36" s="51" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E36" s="52">
-        <x:v>32381</x:v>
-      </x:c>
-      <x:c r="F36" s="53">
-        <x:v>4110</x:v>
-      </x:c>
-      <x:c r="G36" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="53">
-        <x:v>4110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:8">
-      <x:c r="B37" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C37" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D37" s="51" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E37" s="52">
-        <x:v>32382</x:v>
-      </x:c>
-      <x:c r="F37" s="53">
-        <x:v>3117</x:v>
-      </x:c>
-      <x:c r="G37" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="53">
-        <x:v>3117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:8">
-      <x:c r="B38" s="48" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C38" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D38" s="51" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E38" s="52">
-        <x:v>32382</x:v>
-      </x:c>
-      <x:c r="F38" s="53">
-        <x:v>10152</x:v>
-      </x:c>
-      <x:c r="G38" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="53">
-        <x:v>10152</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:8">
-      <x:c r="B39" s="48" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C39" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D39" s="51" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E39" s="52">
-        <x:v>32387</x:v>
-      </x:c>
-      <x:c r="F39" s="53">
-        <x:v>536.8</x:v>
-      </x:c>
-      <x:c r="G39" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="53">
-        <x:v>536.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:8">
-      <x:c r="B40" s="48" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C40" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D40" s="51" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E40" s="52">
-        <x:v>32391</x:v>
-      </x:c>
-      <x:c r="F40" s="53">
-        <x:v>3632</x:v>
-      </x:c>
-      <x:c r="G40" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="53">
-        <x:v>3632</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:8">
-      <x:c r="B41" s="48" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C41" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D41" s="51" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E41" s="52">
-        <x:v>32403</x:v>
-      </x:c>
-      <x:c r="F41" s="53">
-        <x:v>7807</x:v>
-      </x:c>
-      <x:c r="G41" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="53">
-        <x:v>7807</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:8">
-      <x:c r="B42" s="48" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C42" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D42" s="51" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E42" s="52">
-        <x:v>32411</x:v>
-      </x:c>
-      <x:c r="F42" s="53">
-        <x:v>971.7</x:v>
-      </x:c>
-      <x:c r="G42" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="53">
-        <x:v>971.7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:8">
-      <x:c r="B43" s="48" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C43" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D43" s="51" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E43" s="52">
-        <x:v>32417</x:v>
-      </x:c>
-      <x:c r="F43" s="53">
-        <x:v>12455</x:v>
-      </x:c>
-      <x:c r="G43" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="53">
-        <x:v>12455</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:8">
-      <x:c r="B44" s="48" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C44" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D44" s="51" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E44" s="52">
-        <x:v>32425</x:v>
-      </x:c>
-      <x:c r="F44" s="53">
-        <x:v>64050</x:v>
-      </x:c>
-      <x:c r="G44" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="53">
-        <x:v>64050</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:8">
-      <x:c r="B45" s="48" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C45" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D45" s="51" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E45" s="52">
-        <x:v>32433</x:v>
-      </x:c>
-      <x:c r="F45" s="53">
-        <x:v>787.8</x:v>
-      </x:c>
-      <x:c r="G45" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H45" s="53">
-        <x:v>787.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:8">
-      <x:c r="B46" s="48" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C46" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D46" s="51" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E46" s="52">
-        <x:v>32460</x:v>
-      </x:c>
-      <x:c r="F46" s="53">
-        <x:v>766.8</x:v>
-      </x:c>
-      <x:c r="G46" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H46" s="53">
-        <x:v>766.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:8">
-      <x:c r="B47" s="48" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C47" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D47" s="51" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E47" s="52">
-        <x:v>32475</x:v>
-      </x:c>
-      <x:c r="F47" s="53">
-        <x:v>15365</x:v>
-      </x:c>
-      <x:c r="G47" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" s="53">
-        <x:v>15365</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:8">
-      <x:c r="B48" s="48" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C48" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D48" s="51" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="E48" s="52">
-        <x:v>32480</x:v>
-      </x:c>
-      <x:c r="F48" s="53">
-        <x:v>7346</x:v>
-      </x:c>
-      <x:c r="G48" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="53">
-        <x:v>7346</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:8">
-      <x:c r="B49" s="48" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C49" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D49" s="51" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E49" s="52">
-        <x:v>32491</x:v>
-      </x:c>
-      <x:c r="F49" s="53">
-        <x:v>1809.85</x:v>
-      </x:c>
-      <x:c r="G49" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="53">
-        <x:v>1809.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:8">
-      <x:c r="B50" s="48" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C50" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D50" s="51" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E50" s="52">
-        <x:v>32502</x:v>
-      </x:c>
-      <x:c r="F50" s="53">
-        <x:v>6287.85</x:v>
-      </x:c>
-      <x:c r="G50" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H50" s="53">
-        <x:v>6287.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:8">
-      <x:c r="B51" s="48" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C51" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D51" s="51" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E51" s="52">
-        <x:v>32513</x:v>
-      </x:c>
-      <x:c r="F51" s="53">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="G51" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H51" s="53">
-        <x:v>325</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:8">
-      <x:c r="B52" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C52" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D52" s="51" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E52" s="52">
-        <x:v>32515</x:v>
-      </x:c>
-      <x:c r="F52" s="53">
-        <x:v>16788</x:v>
-      </x:c>
-      <x:c r="G52" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H52" s="53">
-        <x:v>16788</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:8">
-      <x:c r="B53" s="48" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C53" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D53" s="51" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E53" s="52">
-        <x:v>32524</x:v>
-      </x:c>
-      <x:c r="F53" s="53">
-        <x:v>24650</x:v>
-      </x:c>
-      <x:c r="G53" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H53" s="53">
-        <x:v>24650</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:8">
-      <x:c r="B54" s="48" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C54" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D54" s="51" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E54" s="52">
-        <x:v>32540</x:v>
-      </x:c>
-      <x:c r="F54" s="53">
-        <x:v>14188</x:v>
-      </x:c>
-      <x:c r="G54" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="53">
-        <x:v>14188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:8">
-      <x:c r="B55" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C55" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D55" s="51" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E55" s="52">
-        <x:v>32544</x:v>
-      </x:c>
-      <x:c r="F55" s="53">
-        <x:v>23406</x:v>
-      </x:c>
-      <x:c r="G55" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="53">
-        <x:v>23406</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:8">
-      <x:c r="B56" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C56" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D56" s="51" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="E56" s="52">
-        <x:v>32548</x:v>
-      </x:c>
-      <x:c r="F56" s="53">
-        <x:v>19293.7</x:v>
-      </x:c>
-      <x:c r="G56" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="53">
-        <x:v>19293.7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:8">
-      <x:c r="B57" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C57" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D57" s="51" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E57" s="52">
-        <x:v>32558</x:v>
-      </x:c>
-      <x:c r="F57" s="53">
-        <x:v>1975</x:v>
-      </x:c>
-      <x:c r="G57" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="53">
-        <x:v>1975</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:8">
-      <x:c r="B58" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C58" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D58" s="51" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E58" s="52">
-        <x:v>32561</x:v>
-      </x:c>
-      <x:c r="F58" s="53">
-        <x:v>12736</x:v>
-      </x:c>
-      <x:c r="G58" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="53">
-        <x:v>12736</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:8">
-      <x:c r="B59" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C59" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D59" s="51" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E59" s="52">
-        <x:v>32564</x:v>
-      </x:c>
-      <x:c r="F59" s="53">
-        <x:v>2150</x:v>
-      </x:c>
-      <x:c r="G59" s="54">
-        <x:v>8.5</x:v>
-      </x:c>
-      <x:c r="H59" s="53">
-        <x:v>2150</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:8">
-      <x:c r="B60" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C60" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D60" s="51" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E60" s="52">
-        <x:v>32568</x:v>
-      </x:c>
-      <x:c r="F60" s="53">
-        <x:v>15355</x:v>
-      </x:c>
-      <x:c r="G60" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H60" s="53">
-        <x:v>15355</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:8">
-      <x:c r="B61" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C61" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D61" s="51" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E61" s="52">
-        <x:v>32571</x:v>
-      </x:c>
-      <x:c r="F61" s="53">
-        <x:v>24277.3</x:v>
-      </x:c>
-      <x:c r="G61" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="53">
-        <x:v>24277.3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:8">
-      <x:c r="B62" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C62" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D62" s="51" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E62" s="52">
-        <x:v>32576</x:v>
-      </x:c>
-      <x:c r="F62" s="53">
-        <x:v>18320</x:v>
-      </x:c>
-      <x:c r="G62" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="53">
-        <x:v>18320</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:8">
-      <x:c r="B63" s="48" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C63" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D63" s="51" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="E63" s="52">
-        <x:v>32581</x:v>
-      </x:c>
-      <x:c r="F63" s="53">
-        <x:v>61869.3</x:v>
-      </x:c>
-      <x:c r="G63" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H63" s="53">
-        <x:v>61869.3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:8">
-      <x:c r="B64" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C64" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D64" s="51" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="E64" s="52">
-        <x:v>32592</x:v>
-      </x:c>
-      <x:c r="F64" s="53">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="G64" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H64" s="53">
-        <x:v>395</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:8">
-      <x:c r="B65" s="48" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C65" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D65" s="51" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E65" s="52">
-        <x:v>32593</x:v>
-      </x:c>
-      <x:c r="F65" s="53">
-        <x:v>17814</x:v>
-      </x:c>
-      <x:c r="G65" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="53">
-        <x:v>17814</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:8">
-      <x:c r="B66" s="48" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C66" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D66" s="51" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="E66" s="52">
-        <x:v>32594</x:v>
-      </x:c>
-      <x:c r="F66" s="53">
-        <x:v>19812</x:v>
-      </x:c>
-      <x:c r="G66" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H66" s="53">
-        <x:v>19812</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:8">
-      <x:c r="B67" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C67" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D67" s="51" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="E67" s="52">
-        <x:v>32600</x:v>
-      </x:c>
-      <x:c r="F67" s="53">
-        <x:v>4495</x:v>
-      </x:c>
-      <x:c r="G67" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H67" s="53">
-        <x:v>4495</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:8">
-      <x:c r="B68" s="48" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C68" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D68" s="51" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E68" s="52">
-        <x:v>32602</x:v>
-      </x:c>
-      <x:c r="F68" s="53">
-        <x:v>31847</x:v>
-      </x:c>
-      <x:c r="G68" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H68" s="53">
-        <x:v>31847</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:8">
-      <x:c r="B69" s="48" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C69" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D69" s="51" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E69" s="52">
-        <x:v>32604</x:v>
-      </x:c>
-      <x:c r="F69" s="53">
-        <x:v>33829.45</x:v>
-      </x:c>
-      <x:c r="G69" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H69" s="53">
-        <x:v>33829.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:8">
-      <x:c r="B70" s="48" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C70" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D70" s="51" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="E70" s="52">
-        <x:v>32606</x:v>
-      </x:c>
-      <x:c r="F70" s="53">
-        <x:v>22354</x:v>
-      </x:c>
-      <x:c r="G70" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H70" s="53">
-        <x:v>22354</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:8">
-      <x:c r="B71" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C71" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D71" s="51" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E71" s="52">
-        <x:v>32608</x:v>
-      </x:c>
-      <x:c r="F71" s="53">
-        <x:v>103041</x:v>
-      </x:c>
-      <x:c r="G71" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H71" s="53">
-        <x:v>103041</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:8">
-      <x:c r="B72" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C72" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D72" s="51" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E72" s="52">
-        <x:v>32610</x:v>
-      </x:c>
-      <x:c r="F72" s="53">
-        <x:v>3596</x:v>
-      </x:c>
-      <x:c r="G72" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H72" s="53">
-        <x:v>3596</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:8">
-      <x:c r="B73" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C73" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D73" s="51" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="E73" s="52">
-        <x:v>32614</x:v>
-      </x:c>
-      <x:c r="F73" s="53">
-        <x:v>19414</x:v>
-      </x:c>
-      <x:c r="G73" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H73" s="53">
-        <x:v>19414</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:8">
-      <x:c r="B74" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C74" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D74" s="51" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="E74" s="52">
-        <x:v>32618</x:v>
-      </x:c>
-      <x:c r="F74" s="53">
-        <x:v>2195</x:v>
-      </x:c>
-      <x:c r="G74" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H74" s="53">
-        <x:v>2195</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:8">
-      <x:c r="B75" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C75" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D75" s="51" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E75" s="52">
-        <x:v>32620</x:v>
-      </x:c>
-      <x:c r="F75" s="53">
-        <x:v>8560</x:v>
-      </x:c>
-      <x:c r="G75" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H75" s="53">
-        <x:v>8560</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:8">
-      <x:c r="B76" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C76" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D76" s="51" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E76" s="52">
-        <x:v>32624</x:v>
-      </x:c>
-      <x:c r="F76" s="53">
-        <x:v>17781</x:v>
-      </x:c>
-      <x:c r="G76" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="53">
-        <x:v>17781</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:8">
-      <x:c r="B77" s="48" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C77" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D77" s="51" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="E77" s="52">
-        <x:v>32629</x:v>
-      </x:c>
-      <x:c r="F77" s="53">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G77" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H77" s="53">
-        <x:v>156</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:8">
-      <x:c r="B78" s="48" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C78" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D78" s="51" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="E78" s="52">
-        <x:v>32630</x:v>
-      </x:c>
-      <x:c r="F78" s="53">
-        <x:v>79116</x:v>
-      </x:c>
-      <x:c r="G78" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H78" s="53">
-        <x:v>79116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:8">
-      <x:c r="B79" s="48" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C79" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D79" s="51" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E79" s="52">
-        <x:v>32632</x:v>
-      </x:c>
-      <x:c r="F79" s="53">
-        <x:v>4445</x:v>
-      </x:c>
-      <x:c r="G79" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H79" s="53">
-        <x:v>4445</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:8">
-      <x:c r="B80" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C80" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D80" s="51" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E80" s="52">
-        <x:v>32634</x:v>
-      </x:c>
-      <x:c r="F80" s="53">
-        <x:v>9634</x:v>
-      </x:c>
-      <x:c r="G80" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H80" s="53">
-        <x:v>9634</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:8">
-      <x:c r="B81" s="48" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C81" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D81" s="51" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="E81" s="52">
-        <x:v>32636</x:v>
-      </x:c>
-      <x:c r="F81" s="53">
-        <x:v>30566</x:v>
-      </x:c>
-      <x:c r="G81" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H81" s="53">
-        <x:v>30566</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:8">
-      <x:c r="B82" s="48" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C82" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D82" s="51" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E82" s="52">
-        <x:v>32638</x:v>
-      </x:c>
-      <x:c r="F82" s="53">
-        <x:v>1416.45</x:v>
-      </x:c>
-      <x:c r="G82" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="53">
-        <x:v>1416.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:8">
-      <x:c r="B83" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C83" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D83" s="51" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E83" s="52">
-        <x:v>32638</x:v>
-      </x:c>
-      <x:c r="F83" s="53">
-        <x:v>11164.8</x:v>
-      </x:c>
-      <x:c r="G83" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H83" s="53">
-        <x:v>11164.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:8">
-      <x:c r="B84" s="48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C84" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D84" s="51" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E84" s="52">
-        <x:v>32640</x:v>
-      </x:c>
-      <x:c r="F84" s="53">
-        <x:v>1185</x:v>
-      </x:c>
-      <x:c r="G84" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H84" s="53">
-        <x:v>1185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:8">
-      <x:c r="B85" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C85" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D85" s="51" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="E85" s="52">
-        <x:v>32647</x:v>
-      </x:c>
-      <x:c r="F85" s="53">
-        <x:v>14049.95</x:v>
-      </x:c>
-      <x:c r="G85" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="53">
-        <x:v>14049.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:8">
-      <x:c r="B86" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C86" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D86" s="51" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E86" s="52">
-        <x:v>32649</x:v>
-      </x:c>
-      <x:c r="F86" s="53">
-        <x:v>14045</x:v>
-      </x:c>
-      <x:c r="G86" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H86" s="53">
-        <x:v>14045</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:8">
-      <x:c r="B87" s="48" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C87" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D87" s="51" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="E87" s="52">
-        <x:v>32651</x:v>
-      </x:c>
-      <x:c r="F87" s="53">
-        <x:v>2706</x:v>
-      </x:c>
-      <x:c r="G87" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H87" s="53">
-        <x:v>2706</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:8">
-      <x:c r="B88" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C88" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D88" s="51" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="E88" s="52">
-        <x:v>32654</x:v>
-      </x:c>
-      <x:c r="F88" s="53">
-        <x:v>8507</x:v>
-      </x:c>
-      <x:c r="G88" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H88" s="53">
-        <x:v>8507</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:8">
-      <x:c r="B89" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C89" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D89" s="51" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="E89" s="52">
-        <x:v>32660</x:v>
-      </x:c>
-      <x:c r="F89" s="53">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="G89" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H89" s="53">
-        <x:v>1950</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:8">
-      <x:c r="B90" s="48" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C90" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D90" s="51" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E90" s="52">
-        <x:v>32660</x:v>
-      </x:c>
-      <x:c r="F90" s="53">
-        <x:v>76698.75</x:v>
-      </x:c>
-      <x:c r="G90" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H90" s="53">
-        <x:v>76698.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:8">
-      <x:c r="B91" s="48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C91" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D91" s="51" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="E91" s="52">
-        <x:v>32661</x:v>
-      </x:c>
-      <x:c r="F91" s="53">
-        <x:v>479.8</x:v>
-      </x:c>
-      <x:c r="G91" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H91" s="53">
-        <x:v>479.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:8">
-      <x:c r="B92" s="48" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C92" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D92" s="51" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E92" s="52">
-        <x:v>32663</x:v>
-      </x:c>
-      <x:c r="F92" s="53">
-        <x:v>4113.75</x:v>
-      </x:c>
-      <x:c r="G92" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H92" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:8">
-      <x:c r="B93" s="48" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C93" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D93" s="51" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="E93" s="52">
-        <x:v>32665</x:v>
-      </x:c>
-      <x:c r="F93" s="53">
-        <x:v>7531.75</x:v>
-      </x:c>
-      <x:c r="G93" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H93" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:8">
-      <x:c r="B94" s="48" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C94" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D94" s="51" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="E94" s="52">
-        <x:v>32668</x:v>
-      </x:c>
-      <x:c r="F94" s="53">
-        <x:v>123740</x:v>
-      </x:c>
-      <x:c r="G94" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H94" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:8">
-      <x:c r="B95" s="48" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C95" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D95" s="51" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E95" s="52">
-        <x:v>32671</x:v>
-      </x:c>
-      <x:c r="F95" s="53">
-        <x:v>12953.6</x:v>
-      </x:c>
-      <x:c r="G95" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H95" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:8">
-      <x:c r="B96" s="48" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C96" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D96" s="51" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="E96" s="52">
-        <x:v>32673</x:v>
-      </x:c>
-      <x:c r="F96" s="53">
-        <x:v>472.9</x:v>
-      </x:c>
-      <x:c r="G96" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H96" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:8">
-      <x:c r="B97" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C97" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D97" s="51" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="E97" s="52">
-        <x:v>32675</x:v>
-      </x:c>
-      <x:c r="F97" s="53">
-        <x:v>859.95</x:v>
-      </x:c>
-      <x:c r="G97" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H97" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:8">
-      <x:c r="B98" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C98" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D98" s="51" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="E98" s="52">
-        <x:v>32679</x:v>
-      </x:c>
-      <x:c r="F98" s="53">
-        <x:v>6094.8</x:v>
-      </x:c>
-      <x:c r="G98" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H98" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:8">
-      <x:c r="B99" s="48" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C99" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D99" s="51" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="E99" s="52">
-        <x:v>32693</x:v>
-      </x:c>
-      <x:c r="F99" s="53">
-        <x:v>11629.85</x:v>
-      </x:c>
-      <x:c r="G99" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H99" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:8">
-      <x:c r="B100" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C100" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D100" s="51" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="E100" s="52">
-        <x:v>33761</x:v>
-      </x:c>
-      <x:c r="F100" s="53">
-        <x:v>2844</x:v>
-      </x:c>
-      <x:c r="G100" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H100" s="53">
-        <x:v>2844</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:8">
-      <x:c r="B101" s="48" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C101" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D101" s="51" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="E101" s="52">
-        <x:v>33798</x:v>
-      </x:c>
-      <x:c r="F101" s="53">
-        <x:v>39797.7</x:v>
-      </x:c>
-      <x:c r="G101" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H101" s="53">
-        <x:v>39797.7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:8">
-      <x:c r="B102" s="48" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C102" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D102" s="51" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="E102" s="52">
-        <x:v>33803</x:v>
-      </x:c>
-      <x:c r="F102" s="53">
-        <x:v>51673.15</x:v>
-      </x:c>
-      <x:c r="G102" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H102" s="53">
-        <x:v>51673.15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:8">
-      <x:c r="B103" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C103" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D103" s="51" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="E103" s="52">
-        <x:v>33806</x:v>
-      </x:c>
-      <x:c r="F103" s="53">
-        <x:v>31219.95</x:v>
-      </x:c>
-      <x:c r="G103" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H103" s="53">
-        <x:v>31219.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:8">
-      <x:c r="B104" s="48" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C104" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D104" s="51" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="E104" s="52">
-        <x:v>33870</x:v>
-      </x:c>
-      <x:c r="F104" s="53">
-        <x:v>3531.8</x:v>
-      </x:c>
-      <x:c r="G104" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H104" s="53">
-        <x:v>3531.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:8">
-      <x:c r="B105" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C105" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D105" s="51" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="E105" s="52">
-        <x:v>33901</x:v>
-      </x:c>
-      <x:c r="F105" s="53">
-        <x:v>28389</x:v>
-      </x:c>
-      <x:c r="G105" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H105" s="53">
-        <x:v>28389</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:8">
-      <x:c r="B106" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C106" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D106" s="51" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="E106" s="52">
-        <x:v>33921</x:v>
-      </x:c>
-      <x:c r="F106" s="53">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G106" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H106" s="53">
-        <x:v>203</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:8">
-      <x:c r="B107" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C107" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D107" s="51" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="E107" s="52">
-        <x:v>33952</x:v>
-      </x:c>
-      <x:c r="F107" s="53">
-        <x:v>4720.8</x:v>
-      </x:c>
-      <x:c r="G107" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H107" s="53">
-        <x:v>4720.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:8">
-      <x:c r="B108" s="48" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C108" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D108" s="51" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="E108" s="52">
-        <x:v>33971</x:v>
-      </x:c>
-      <x:c r="F108" s="53">
-        <x:v>5565</x:v>
-      </x:c>
-      <x:c r="G108" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H108" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:8">
-      <x:c r="B109" s="48" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C109" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D109" s="51" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E109" s="52">
-        <x:v>34012</x:v>
-      </x:c>
-      <x:c r="F109" s="53">
-        <x:v>2514.65</x:v>
-      </x:c>
-      <x:c r="G109" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H109" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:8">
-      <x:c r="B110" s="48" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C110" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D110" s="51" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="E110" s="52">
-        <x:v>34041</x:v>
-      </x:c>
-      <x:c r="F110" s="53">
-        <x:v>4894.95</x:v>
-      </x:c>
-      <x:c r="G110" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H110" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:8">
-      <x:c r="B111" s="48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C111" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D111" s="51" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="E111" s="52">
-        <x:v>34049</x:v>
-      </x:c>
-      <x:c r="F111" s="53">
-        <x:v>23104</x:v>
-      </x:c>
-      <x:c r="G111" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H111" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:8">
-      <x:c r="B112" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C112" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D112" s="51" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="E112" s="52">
-        <x:v>34072</x:v>
-      </x:c>
-      <x:c r="F112" s="53">
-        <x:v>6734.85</x:v>
-      </x:c>
-      <x:c r="G112" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H112" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:8">
-      <x:c r="B113" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C113" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D113" s="51" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="E113" s="52">
-        <x:v>34082</x:v>
-      </x:c>
-      <x:c r="F113" s="53">
-        <x:v>21614</x:v>
-      </x:c>
-      <x:c r="G113" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H113" s="53">
-        <x:v>21614</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:8">
-      <x:c r="B114" s="48" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C114" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D114" s="51" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="E114" s="52">
-        <x:v>34104</x:v>
-      </x:c>
-      <x:c r="F114" s="53">
-        <x:v>14557.95</x:v>
-      </x:c>
-      <x:c r="G114" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H114" s="53">
-        <x:v>14557.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:8">
-      <x:c r="B115" s="48" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C115" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D115" s="51" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="E115" s="52">
-        <x:v>34114</x:v>
-      </x:c>
-      <x:c r="F115" s="53">
-        <x:v>784.9</x:v>
-      </x:c>
-      <x:c r="G115" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H115" s="53">
-        <x:v>784.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:8">
-      <x:c r="B116" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C116" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D116" s="51" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="E116" s="52">
-        <x:v>34122</x:v>
-      </x:c>
-      <x:c r="F116" s="53">
-        <x:v>820</x:v>
-      </x:c>
-      <x:c r="G116" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H116" s="53">
-        <x:v>820</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:8">
-      <x:c r="B117" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C117" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D117" s="51" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="E117" s="52">
-        <x:v>34173</x:v>
-      </x:c>
-      <x:c r="F117" s="53">
-        <x:v>44854</x:v>
-      </x:c>
-      <x:c r="G117" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H117" s="53">
-        <x:v>44854</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:8">
-      <x:c r="B118" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C118" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D118" s="51" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="E118" s="52">
-        <x:v>34205</x:v>
-      </x:c>
-      <x:c r="F118" s="53">
-        <x:v>13945</x:v>
-      </x:c>
-      <x:c r="G118" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H118" s="53">
-        <x:v>13945</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:8">
-      <x:c r="B119" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C119" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D119" s="51" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="E119" s="52">
-        <x:v>34213</x:v>
-      </x:c>
-      <x:c r="F119" s="53">
-        <x:v>33071</x:v>
-      </x:c>
-      <x:c r="G119" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H119" s="53">
-        <x:v>33071</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:8">
-      <x:c r="B120" s="48" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C120" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D120" s="51" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="E120" s="52">
-        <x:v>34216</x:v>
-      </x:c>
-      <x:c r="F120" s="53">
-        <x:v>6583.8</x:v>
-      </x:c>
-      <x:c r="G120" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H120" s="53">
-        <x:v>6583.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:8">
-      <x:c r="B121" s="48" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C121" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D121" s="51" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="E121" s="52">
-        <x:v>34243</x:v>
-      </x:c>
-      <x:c r="F121" s="53">
-        <x:v>10107</x:v>
-      </x:c>
-      <x:c r="G121" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H121" s="53">
-        <x:v>10107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:8">
-      <x:c r="B122" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C122" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D122" s="51" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="E122" s="52">
-        <x:v>34244</x:v>
-      </x:c>
-      <x:c r="F122" s="53">
-        <x:v>25071</x:v>
-      </x:c>
-      <x:c r="G122" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H122" s="53">
-        <x:v>25071</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:8">
-      <x:c r="B123" s="48" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C123" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D123" s="51" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="E123" s="52">
-        <x:v>34250</x:v>
-      </x:c>
-      <x:c r="F123" s="53">
-        <x:v>8294</x:v>
-      </x:c>
-      <x:c r="G123" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H123" s="53">
-        <x:v>8294</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:8">
-      <x:c r="B124" s="48" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C124" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D124" s="51" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="E124" s="52">
-        <x:v>34261</x:v>
-      </x:c>
-      <x:c r="F124" s="53">
-        <x:v>1004.8</x:v>
-      </x:c>
-      <x:c r="G124" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H124" s="53">
-        <x:v>1004.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:8">
-      <x:c r="B125" s="48" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="C125" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D125" s="51" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="E125" s="52">
-        <x:v>34268</x:v>
-      </x:c>
-      <x:c r="F125" s="53">
-        <x:v>6300</x:v>
-      </x:c>
-      <x:c r="G125" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H125" s="53">
-        <x:v>6300</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:8">
-      <x:c r="B126" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C126" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D126" s="51" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="E126" s="52">
-        <x:v>34274</x:v>
-      </x:c>
-      <x:c r="F126" s="53">
-        <x:v>11989.2</x:v>
-      </x:c>
-      <x:c r="G126" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H126" s="53">
-        <x:v>11989.2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:8">
-      <x:c r="B127" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C127" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D127" s="51" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E127" s="52">
-        <x:v>34274</x:v>
-      </x:c>
-      <x:c r="F127" s="53">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="G127" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H127" s="53">
-        <x:v>906</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:8">
-      <x:c r="B128" s="48" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C128" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D128" s="51" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E128" s="52">
-        <x:v>34275</x:v>
-      </x:c>
-      <x:c r="F128" s="53">
-        <x:v>2419</x:v>
-      </x:c>
-      <x:c r="G128" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H128" s="53">
-        <x:v>2419</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:8">
-      <x:c r="B129" s="48" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="C129" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D129" s="51" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="E129" s="52">
-        <x:v>34287</x:v>
-      </x:c>
-      <x:c r="F129" s="53">
-        <x:v>6675.95</x:v>
-      </x:c>
-      <x:c r="G129" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H129" s="53">
-        <x:v>6675.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:8">
-      <x:c r="B130" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C130" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D130" s="51" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="E130" s="52">
-        <x:v>34300</x:v>
-      </x:c>
-      <x:c r="F130" s="53">
-        <x:v>2971</x:v>
-      </x:c>
-      <x:c r="G130" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H130" s="53">
-        <x:v>2971</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:8">
-      <x:c r="B131" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C131" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D131" s="51" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="E131" s="52">
-        <x:v>34300</x:v>
-      </x:c>
-      <x:c r="F131" s="53">
-        <x:v>6785.4</x:v>
-      </x:c>
-      <x:c r="G131" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H131" s="53">
-        <x:v>6785.4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:8">
-      <x:c r="B132" s="48" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C132" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D132" s="51" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E132" s="52">
-        <x:v>34304</x:v>
-      </x:c>
-      <x:c r="F132" s="53">
-        <x:v>47710.75</x:v>
-      </x:c>
-      <x:c r="G132" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H132" s="53">
-        <x:v>47710.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:8">
-      <x:c r="B133" s="48" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C133" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D133" s="51" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="E133" s="52">
-        <x:v>34315</x:v>
-      </x:c>
-      <x:c r="F133" s="53">
-        <x:v>1240</x:v>
-      </x:c>
-      <x:c r="G133" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H133" s="53">
-        <x:v>1240</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:8">
-      <x:c r="B134" s="48" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C134" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D134" s="51" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="E134" s="52">
-        <x:v>34320</x:v>
-      </x:c>
-      <x:c r="F134" s="53">
-        <x:v>1846</x:v>
-      </x:c>
-      <x:c r="G134" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H134" s="53">
-        <x:v>1846</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:8">
-      <x:c r="B135" s="48" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C135" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D135" s="51" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="E135" s="52">
-        <x:v>34328</x:v>
-      </x:c>
-      <x:c r="F135" s="53">
-        <x:v>3546</x:v>
-      </x:c>
-      <x:c r="G135" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H135" s="53">
-        <x:v>3546</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:8">
-      <x:c r="B136" s="48" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C136" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D136" s="51" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="E136" s="52">
-        <x:v>34335</x:v>
-      </x:c>
-      <x:c r="F136" s="53">
-        <x:v>3087</x:v>
-      </x:c>
-      <x:c r="G136" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H136" s="53">
-        <x:v>3087</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:8">
-      <x:c r="B137" s="48" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C137" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D137" s="51" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="E137" s="52">
-        <x:v>34343</x:v>
-      </x:c>
-      <x:c r="F137" s="53">
-        <x:v>10054</x:v>
-      </x:c>
-      <x:c r="G137" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H137" s="53">
-        <x:v>10054</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:8">
-      <x:c r="B138" s="48" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C138" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D138" s="51" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="E138" s="52">
-        <x:v>34351</x:v>
-      </x:c>
-      <x:c r="F138" s="53">
-        <x:v>4229.8</x:v>
-      </x:c>
-      <x:c r="G138" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H138" s="53">
-        <x:v>4229.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:8">
-      <x:c r="B139" s="48" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C139" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D139" s="51" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="E139" s="52">
-        <x:v>34378</x:v>
-      </x:c>
-      <x:c r="F139" s="53">
-        <x:v>15052</x:v>
-      </x:c>
-      <x:c r="G139" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H139" s="53">
-        <x:v>15052</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:8">
-      <x:c r="B140" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C140" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D140" s="51" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="E140" s="52">
-        <x:v>34396</x:v>
-      </x:c>
-      <x:c r="F140" s="53">
-        <x:v>5011</x:v>
-      </x:c>
-      <x:c r="G140" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H140" s="53">
-        <x:v>5011</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:8">
-      <x:c r="B141" s="48" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C141" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D141" s="51" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="E141" s="52">
-        <x:v>34407</x:v>
-      </x:c>
-      <x:c r="F141" s="53">
-        <x:v>12900.75</x:v>
-      </x:c>
-      <x:c r="G141" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H141" s="53">
-        <x:v>12900.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:8">
-      <x:c r="B142" s="48" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C142" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D142" s="51" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="E142" s="52">
-        <x:v>34418</x:v>
-      </x:c>
-      <x:c r="F142" s="53">
-        <x:v>7671.9</x:v>
-      </x:c>
-      <x:c r="G142" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H142" s="53">
-        <x:v>7671.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:8">
-      <x:c r="B143" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C143" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D143" s="51" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="E143" s="52">
-        <x:v>34431</x:v>
-      </x:c>
-      <x:c r="F143" s="53">
-        <x:v>97698.6</x:v>
-      </x:c>
-      <x:c r="G143" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H143" s="53">
-        <x:v>97698.6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:8">
-      <x:c r="B144" s="48" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C144" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D144" s="51" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="E144" s="52">
-        <x:v>34440</x:v>
-      </x:c>
-      <x:c r="F144" s="53">
-        <x:v>3860.85</x:v>
-      </x:c>
-      <x:c r="G144" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H144" s="53">
-        <x:v>3860.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:8">
-      <x:c r="B145" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C145" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D145" s="51" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="E145" s="52">
-        <x:v>34455</x:v>
-      </x:c>
-      <x:c r="F145" s="53">
-        <x:v>13226.8</x:v>
-      </x:c>
-      <x:c r="G145" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H145" s="53">
-        <x:v>13226.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:8">
-      <x:c r="B146" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C146" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D146" s="51" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="E146" s="52">
-        <x:v>34459</x:v>
-      </x:c>
-      <x:c r="F146" s="53">
-        <x:v>13935.95</x:v>
-      </x:c>
-      <x:c r="G146" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H146" s="53">
-        <x:v>13935.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:8">
-      <x:c r="B147" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C147" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D147" s="51" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="E147" s="52">
-        <x:v>34463</x:v>
-      </x:c>
-      <x:c r="F147" s="53">
-        <x:v>12367</x:v>
-      </x:c>
-      <x:c r="G147" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H147" s="53">
-        <x:v>12367</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:8">
-      <x:c r="B148" s="48" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C148" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D148" s="51" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="E148" s="52">
-        <x:v>34476</x:v>
-      </x:c>
-      <x:c r="F148" s="53">
-        <x:v>9793.55</x:v>
-      </x:c>
-      <x:c r="G148" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H148" s="53">
-        <x:v>9793.55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:8">
-      <x:c r="B149" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C149" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D149" s="51" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="E149" s="52">
-        <x:v>34486</x:v>
-      </x:c>
-      <x:c r="F149" s="53">
-        <x:v>2206.85</x:v>
-      </x:c>
-      <x:c r="G149" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H149" s="53">
-        <x:v>2206.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:8">
-      <x:c r="B150" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C150" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D150" s="51" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="E150" s="52">
-        <x:v>34489</x:v>
-      </x:c>
-      <x:c r="F150" s="53">
-        <x:v>102453.6</x:v>
-      </x:c>
-      <x:c r="G150" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H150" s="53">
-        <x:v>102453.6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:8">
-      <x:c r="B151" s="48" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C151" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D151" s="51" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="E151" s="52">
-        <x:v>34494</x:v>
-      </x:c>
-      <x:c r="F151" s="53">
-        <x:v>3153</x:v>
-      </x:c>
-      <x:c r="G151" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H151" s="53">
-        <x:v>3153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:8">
-      <x:c r="B152" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C152" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D152" s="51" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="E152" s="52">
-        <x:v>34499</x:v>
-      </x:c>
-      <x:c r="F152" s="53">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="G152" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H152" s="53">
-        <x:v>342</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:8">
-      <x:c r="B153" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C153" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D153" s="51" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="E153" s="52">
-        <x:v>34511</x:v>
-      </x:c>
-      <x:c r="F153" s="53">
-        <x:v>2692.85</x:v>
-      </x:c>
-      <x:c r="G153" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H153" s="53">
-        <x:v>2692.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:8">
-      <x:c r="B154" s="48" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C154" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D154" s="51" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E154" s="52">
-        <x:v>34516</x:v>
-      </x:c>
-      <x:c r="F154" s="53">
-        <x:v>28862</x:v>
-      </x:c>
-      <x:c r="G154" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H154" s="53">
-        <x:v>28862</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:8">
-      <x:c r="B155" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C155" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D155" s="51" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="E155" s="52">
-        <x:v>34519</x:v>
-      </x:c>
-      <x:c r="F155" s="53">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G155" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H155" s="53">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" spans="1:8">
-      <x:c r="B156" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C156" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D156" s="51" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="E156" s="52">
-        <x:v>34521</x:v>
-      </x:c>
-      <x:c r="F156" s="53">
-        <x:v>9471.95</x:v>
-      </x:c>
-      <x:c r="G156" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H156" s="53">
-        <x:v>9471.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:8">
-      <x:c r="B157" s="48" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C157" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D157" s="51" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="E157" s="52">
-        <x:v>34523</x:v>
-      </x:c>
-      <x:c r="F157" s="53">
-        <x:v>5654.8</x:v>
-      </x:c>
-      <x:c r="G157" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H157" s="53">
-        <x:v>5654.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:8">
-      <x:c r="B158" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C158" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D158" s="51" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="E158" s="52">
-        <x:v>34525</x:v>
-      </x:c>
-      <x:c r="F158" s="53">
-        <x:v>2356.9</x:v>
-      </x:c>
-      <x:c r="G158" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H158" s="53">
-        <x:v>2356.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:8">
-      <x:c r="B159" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C159" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D159" s="51" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="E159" s="52">
-        <x:v>34531</x:v>
-      </x:c>
-      <x:c r="F159" s="53">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G159" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H159" s="53">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:8">
-      <x:c r="B160" s="48" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C160" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D160" s="51" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="E160" s="52">
-        <x:v>34537</x:v>
-      </x:c>
-      <x:c r="F160" s="53">
-        <x:v>13814.05</x:v>
-      </x:c>
-      <x:c r="G160" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H160" s="53">
-        <x:v>13814.05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:8">
-      <x:c r="B161" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C161" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D161" s="51" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="E161" s="52">
-        <x:v>34541</x:v>
-      </x:c>
-      <x:c r="F161" s="53">
-        <x:v>4178.85</x:v>
-      </x:c>
-      <x:c r="G161" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H161" s="53">
-        <x:v>4178.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:8">
-      <x:c r="B162" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C162" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D162" s="51" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="E162" s="52">
-        <x:v>34548</x:v>
-      </x:c>
-      <x:c r="F162" s="53">
-        <x:v>5511.75</x:v>
-      </x:c>
-      <x:c r="G162" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H162" s="53">
-        <x:v>5511.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:8">
-      <x:c r="B163" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C163" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D163" s="51" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="E163" s="52">
-        <x:v>34552</x:v>
-      </x:c>
-      <x:c r="F163" s="53">
-        <x:v>3640</x:v>
-      </x:c>
-      <x:c r="G163" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H163" s="53">
-        <x:v>3640</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:8">
-      <x:c r="B164" s="48" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C164" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D164" s="51" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="E164" s="52">
-        <x:v>34556</x:v>
-      </x:c>
-      <x:c r="F164" s="53">
-        <x:v>3650</x:v>
-      </x:c>
-      <x:c r="G164" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H164" s="53">
-        <x:v>3650</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:8">
-      <x:c r="B165" s="48" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C165" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D165" s="51" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="E165" s="52">
-        <x:v>34583</x:v>
-      </x:c>
-      <x:c r="F165" s="53">
-        <x:v>7868</x:v>
-      </x:c>
-      <x:c r="G165" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H165" s="53">
-        <x:v>7868</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:8">
-      <x:c r="B166" s="48" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C166" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D166" s="51" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="E166" s="52">
-        <x:v>34585</x:v>
-      </x:c>
-      <x:c r="F166" s="53">
-        <x:v>5983</x:v>
-      </x:c>
-      <x:c r="G166" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H166" s="53">
-        <x:v>5983</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:8">
-      <x:c r="B167" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C167" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D167" s="51" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="E167" s="52">
-        <x:v>34589</x:v>
-      </x:c>
-      <x:c r="F167" s="53">
-        <x:v>6731</x:v>
-      </x:c>
-      <x:c r="G167" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H167" s="53">
-        <x:v>6731</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:8">
-      <x:c r="B168" s="48" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C168" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D168" s="51" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="E168" s="52">
-        <x:v>34591</x:v>
-      </x:c>
-      <x:c r="F168" s="53">
-        <x:v>72089.9</x:v>
-      </x:c>
-      <x:c r="G168" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H168" s="53">
-        <x:v>72089.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:8">
-      <x:c r="B169" s="48" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C169" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D169" s="51" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="E169" s="52">
-        <x:v>34593</x:v>
-      </x:c>
-      <x:c r="F169" s="53">
-        <x:v>716</x:v>
-      </x:c>
-      <x:c r="G169" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H169" s="53">
-        <x:v>716</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:8">
-      <x:c r="B170" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C170" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D170" s="51" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="E170" s="52">
-        <x:v>34597</x:v>
-      </x:c>
-      <x:c r="F170" s="53">
-        <x:v>1827</x:v>
-      </x:c>
-      <x:c r="G170" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H170" s="53">
-        <x:v>1827</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:8">
-      <x:c r="B171" s="48" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="C171" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D171" s="51" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="E171" s="52">
-        <x:v>34611</x:v>
-      </x:c>
-      <x:c r="F171" s="53">
-        <x:v>7990</x:v>
-      </x:c>
-      <x:c r="G171" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H171" s="53">
-        <x:v>7990</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:8">
-      <x:c r="B172" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C172" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D172" s="51" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="E172" s="52">
-        <x:v>34613</x:v>
-      </x:c>
-      <x:c r="F172" s="53">
-        <x:v>4205</x:v>
-      </x:c>
-      <x:c r="G172" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H172" s="53">
-        <x:v>4205</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:8">
-      <x:c r="B173" s="48" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C173" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D173" s="51" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E173" s="52">
-        <x:v>34625</x:v>
-      </x:c>
-      <x:c r="F173" s="53">
-        <x:v>10263.75</x:v>
-      </x:c>
-      <x:c r="G173" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H173" s="53">
-        <x:v>10263.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:8">
-      <x:c r="B174" s="48" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C174" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D174" s="51" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="E174" s="52">
-        <x:v>34628</x:v>
-      </x:c>
-      <x:c r="F174" s="53">
-        <x:v>4029.55</x:v>
-      </x:c>
-      <x:c r="G174" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H174" s="53">
-        <x:v>4029.55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:8">
-      <x:c r="B175" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C175" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D175" s="51" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="E175" s="52">
-        <x:v>34649</x:v>
-      </x:c>
-      <x:c r="F175" s="53">
-        <x:v>12949.7</x:v>
-      </x:c>
-      <x:c r="G175" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H175" s="53">
-        <x:v>12949.7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:8">
-      <x:c r="B176" s="48" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C176" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D176" s="51" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="E176" s="52">
-        <x:v>34650</x:v>
-      </x:c>
-      <x:c r="F176" s="53">
-        <x:v>20711.9</x:v>
-      </x:c>
-      <x:c r="G176" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H176" s="53">
-        <x:v>20711.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:8">
-      <x:c r="B177" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C177" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D177" s="51" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="E177" s="52">
-        <x:v>34652</x:v>
-      </x:c>
-      <x:c r="F177" s="53">
-        <x:v>3975.75</x:v>
-      </x:c>
-      <x:c r="G177" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H177" s="53">
-        <x:v>3975.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:8">
-      <x:c r="B178" s="48" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C178" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D178" s="51" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="E178" s="52">
-        <x:v>34654</x:v>
-      </x:c>
-      <x:c r="F178" s="53">
-        <x:v>8305.95</x:v>
-      </x:c>
-      <x:c r="G178" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H178" s="53">
-        <x:v>8305.95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:8">
-      <x:c r="B179" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C179" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D179" s="51" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="E179" s="52">
-        <x:v>34660</x:v>
-      </x:c>
-      <x:c r="F179" s="53">
-        <x:v>51730.8</x:v>
-      </x:c>
-      <x:c r="G179" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H179" s="53">
-        <x:v>51730.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:8">
-      <x:c r="B180" s="48" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C180" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D180" s="51" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="E180" s="52">
-        <x:v>34661</x:v>
-      </x:c>
-      <x:c r="F180" s="53">
-        <x:v>2099</x:v>
-      </x:c>
-      <x:c r="G180" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H180" s="53">
-        <x:v>2099</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:8">
-      <x:c r="B181" s="48" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C181" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D181" s="51" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="E181" s="52">
-        <x:v>34662</x:v>
-      </x:c>
-      <x:c r="F181" s="53">
-        <x:v>45160.1</x:v>
-      </x:c>
-      <x:c r="G181" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H181" s="53">
-        <x:v>45160.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:8">
-      <x:c r="B182" s="48" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C182" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D182" s="51" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="E182" s="52">
-        <x:v>34664</x:v>
-      </x:c>
-      <x:c r="F182" s="53">
-        <x:v>4774.85</x:v>
-      </x:c>
-      <x:c r="G182" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H182" s="53">
-        <x:v>4774.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:8">
-      <x:c r="B183" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C183" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D183" s="51" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="E183" s="52">
-        <x:v>34677</x:v>
-      </x:c>
-      <x:c r="F183" s="53">
-        <x:v>64115.75</x:v>
-      </x:c>
-      <x:c r="G183" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H183" s="53">
-        <x:v>64115.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:8">
-      <x:c r="B184" s="48" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C184" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D184" s="51" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="E184" s="52">
-        <x:v>34678</x:v>
-      </x:c>
-      <x:c r="F184" s="53">
-        <x:v>2577.85</x:v>
-      </x:c>
-      <x:c r="G184" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H184" s="53">
-        <x:v>2577.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:8">
-      <x:c r="B185" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C185" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D185" s="51" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="E185" s="52">
-        <x:v>34679</x:v>
-      </x:c>
-      <x:c r="F185" s="53">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="G185" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H185" s="53">
-        <x:v>1999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:8">
-      <x:c r="B186" s="48" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C186" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D186" s="51" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="E186" s="52">
-        <x:v>34682</x:v>
-      </x:c>
-      <x:c r="F186" s="53">
-        <x:v>158922.65</x:v>
-      </x:c>
-      <x:c r="G186" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H186" s="53">
-        <x:v>158922.65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:8">
-      <x:c r="B187" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C187" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D187" s="51" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="E187" s="52">
-        <x:v>34683</x:v>
-      </x:c>
-      <x:c r="F187" s="53">
-        <x:v>6935</x:v>
-      </x:c>
-      <x:c r="G187" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H187" s="53">
-        <x:v>6935</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:8">
-      <x:c r="B188" s="48" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C188" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D188" s="51" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="E188" s="52">
-        <x:v>34684</x:v>
-      </x:c>
-      <x:c r="F188" s="53">
-        <x:v>1400</x:v>
-      </x:c>
-      <x:c r="G188" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H188" s="53">
-        <x:v>1400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:8">
-      <x:c r="B189" s="48" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C189" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D189" s="51" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="E189" s="52">
-        <x:v>34688</x:v>
-      </x:c>
-      <x:c r="F189" s="53">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="G189" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H189" s="53">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:8">
-      <x:c r="B190" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C190" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D190" s="51" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="E190" s="52">
-        <x:v>34690</x:v>
-      </x:c>
-      <x:c r="F190" s="53">
-        <x:v>16939.5</x:v>
-      </x:c>
-      <x:c r="G190" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H190" s="53">
-        <x:v>16939.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:8">
-      <x:c r="B191" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C191" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D191" s="51" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="E191" s="52">
-        <x:v>34691</x:v>
-      </x:c>
-      <x:c r="F191" s="53">
-        <x:v>11568</x:v>
-      </x:c>
-      <x:c r="G191" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H191" s="53">
-        <x:v>11568</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:8">
-      <x:c r="B192" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C192" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D192" s="51" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="E192" s="52">
-        <x:v>34694</x:v>
-      </x:c>
-      <x:c r="F192" s="53">
-        <x:v>4317.75</x:v>
-      </x:c>
-      <x:c r="G192" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H192" s="53">
-        <x:v>4317.75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:8">
-      <x:c r="B193" s="48" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C193" s="51" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D193" s="51" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="E193" s="52">
-        <x:v>34698</x:v>
-      </x:c>
-      <x:c r="F193" s="53">
-        <x:v>7134</x:v>
-      </x:c>
-      <x:c r="G193" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H193" s="53">
-        <x:v>7134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:8">
-      <x:c r="B194" s="48" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C194" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D194" s="51" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="E194" s="52">
-        <x:v>34700</x:v>
-      </x:c>
-      <x:c r="F194" s="53">
-        <x:v>7986.9</x:v>
-      </x:c>
-      <x:c r="G194" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H194" s="53">
-        <x:v>7986.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:8">
-      <x:c r="B195" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C195" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D195" s="51" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="E195" s="52">
-        <x:v>34703</x:v>
-      </x:c>
-      <x:c r="F195" s="53">
-        <x:v>3304.85</x:v>
-      </x:c>
-      <x:c r="G195" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H195" s="53">
-        <x:v>3304.85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:8">
-      <x:c r="B196" s="48" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C196" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D196" s="51" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="E196" s="52">
-        <x:v>34705</x:v>
-      </x:c>
-      <x:c r="F196" s="53">
-        <x:v>17917</x:v>
-      </x:c>
-      <x:c r="G196" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H196" s="53">
-        <x:v>17917</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:8">
-      <x:c r="B197" s="48" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="C197" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D197" s="51" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="E197" s="52">
-        <x:v>34707</x:v>
-      </x:c>
-      <x:c r="F197" s="53">
-        <x:v>7423.35</x:v>
-      </x:c>
-      <x:c r="G197" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H197" s="53">
-        <x:v>7423.35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:8">
-      <x:c r="B198" s="48" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C198" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D198" s="51" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="E198" s="52">
-        <x:v>34708</x:v>
-      </x:c>
-      <x:c r="F198" s="53">
-        <x:v>9897</x:v>
-      </x:c>
-      <x:c r="G198" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H198" s="53">
-        <x:v>9897</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:8">
-      <x:c r="B199" s="48" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C199" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D199" s="51" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="E199" s="52">
-        <x:v>34709</x:v>
-      </x:c>
-      <x:c r="F199" s="53">
-        <x:v>52729.25</x:v>
-      </x:c>
-      <x:c r="G199" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H199" s="53">
-        <x:v>52729.25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:8">
-      <x:c r="B200" s="48" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C200" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D200" s="51" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="E200" s="52">
-        <x:v>34715</x:v>
-      </x:c>
-      <x:c r="F200" s="53">
-        <x:v>24485</x:v>
-      </x:c>
-      <x:c r="G200" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H200" s="53">
-        <x:v>24485</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:8">
-      <x:c r="B201" s="48" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C201" s="51" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D201" s="51" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="E201" s="52">
-        <x:v>34719</x:v>
-      </x:c>
-      <x:c r="F201" s="53">
-        <x:v>3065</x:v>
-      </x:c>
-      <x:c r="G201" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H201" s="53">
-        <x:v>3065</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:8">
-      <x:c r="B202" s="48" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C202" s="51" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D202" s="51" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="E202" s="52">
-        <x:v>34721</x:v>
-      </x:c>
-      <x:c r="F202" s="53">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="G202" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H202" s="53">
-        <x:v>465</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:8">
-      <x:c r="B203" s="48" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C203" s="51" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D203" s="51" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="E203" s="52">
-        <x:v>34725</x:v>
-      </x:c>
-      <x:c r="F203" s="53">
-        <x:v>5037.1</x:v>
-      </x:c>
-      <x:c r="G203" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H203" s="53">
-        <x:v>5037.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:8">
-      <x:c r="B204" s="48" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C204" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D204" s="51" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="E204" s="52">
-        <x:v>34731</x:v>
-      </x:c>
-      <x:c r="F204" s="53">
-        <x:v>7572</x:v>
-      </x:c>
-      <x:c r="G204" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H204" s="53">
-        <x:v>7572</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:8">
-      <x:c r="B205" s="48" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C205" s="51" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D205" s="51" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="E205" s="52">
-        <x:v>34732</x:v>
-      </x:c>
-      <x:c r="F205" s="53">
-        <x:v>8939.6</x:v>
-      </x:c>
-      <x:c r="G205" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H205" s="53">
-        <x:v>8939.6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:8">
-      <x:c r="B206" s="48" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="C206" s="51" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D206" s="51" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="E206" s="52">
-        <x:v>34735</x:v>
-      </x:c>
-      <x:c r="F206" s="53">
-        <x:v>13908</x:v>
-      </x:c>
-      <x:c r="G206" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H206" s="53">
-        <x:v>13908</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:8">
-      <x:c r="B207" s="48" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C207" s="51" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D207" s="51" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="E207" s="52"/>
-      <x:c r="F207" s="53">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G207" s="54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H207" s="53">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="2" spans="1:8" ht="30.75" customHeight="1">
+      <c r="B2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="52">
+        <v>32266</v>
+      </c>
+      <c r="F3" s="53">
+        <v>1250</v>
+      </c>
+      <c r="G3" s="54">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="52">
+        <v>32251</v>
+      </c>
+      <c r="F4" s="53">
+        <v>7885</v>
+      </c>
+      <c r="G4" s="54">
+        <v>0</v>
+      </c>
+      <c r="H4" s="53">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="52">
+        <v>32163</v>
+      </c>
+      <c r="F5" s="53">
+        <v>4807</v>
+      </c>
+      <c r="G5" s="54">
+        <v>0</v>
+      </c>
+      <c r="H5" s="53">
+        <v>4807</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="52">
+        <v>32454</v>
+      </c>
+      <c r="F6" s="53">
+        <v>31987</v>
+      </c>
+      <c r="G6" s="54">
+        <v>0</v>
+      </c>
+      <c r="H6" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="52">
+        <v>32265</v>
+      </c>
+      <c r="F7" s="53">
+        <v>6500</v>
+      </c>
+      <c r="G7" s="54">
+        <v>0</v>
+      </c>
+      <c r="H7" s="53">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="52">
+        <v>32267</v>
+      </c>
+      <c r="F8" s="53">
+        <v>1449.5</v>
+      </c>
+      <c r="G8" s="54">
+        <v>0</v>
+      </c>
+      <c r="H8" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="52">
+        <v>32275</v>
+      </c>
+      <c r="F9" s="53">
+        <v>5587</v>
+      </c>
+      <c r="G9" s="54">
+        <v>0</v>
+      </c>
+      <c r="H9" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="52">
+        <v>32275</v>
+      </c>
+      <c r="F10" s="53">
+        <v>4996</v>
+      </c>
+      <c r="G10" s="54">
+        <v>0</v>
+      </c>
+      <c r="H10" s="53">
+        <v>4996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="52">
+        <v>32282</v>
+      </c>
+      <c r="F11" s="53">
+        <v>2679.85</v>
+      </c>
+      <c r="G11" s="54">
+        <v>0</v>
+      </c>
+      <c r="H11" s="53">
+        <v>2679.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="52">
+        <v>32283</v>
+      </c>
+      <c r="F12" s="53">
+        <v>5201</v>
+      </c>
+      <c r="G12" s="54">
+        <v>0</v>
+      </c>
+      <c r="H12" s="53">
+        <v>5201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="52">
+        <v>32289</v>
+      </c>
+      <c r="F13" s="53">
+        <v>3115</v>
+      </c>
+      <c r="G13" s="54">
+        <v>0</v>
+      </c>
+      <c r="H13" s="53">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="52">
+        <v>32289</v>
+      </c>
+      <c r="F14" s="53">
+        <v>134.85</v>
+      </c>
+      <c r="G14" s="54">
+        <v>0</v>
+      </c>
+      <c r="H14" s="53">
+        <v>134.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="52">
+        <v>32289</v>
+      </c>
+      <c r="F15" s="53">
+        <v>20321.75</v>
+      </c>
+      <c r="G15" s="54">
+        <v>0</v>
+      </c>
+      <c r="H15" s="53">
+        <v>20321.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="52">
+        <v>32297</v>
+      </c>
+      <c r="F16" s="53">
+        <v>2605</v>
+      </c>
+      <c r="G16" s="54">
+        <v>0</v>
+      </c>
+      <c r="H16" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="52">
+        <v>32307</v>
+      </c>
+      <c r="F17" s="53">
+        <v>10195</v>
+      </c>
+      <c r="G17" s="54">
+        <v>0</v>
+      </c>
+      <c r="H17" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="52">
+        <v>32313</v>
+      </c>
+      <c r="F18" s="53">
+        <v>5256</v>
+      </c>
+      <c r="G18" s="54">
+        <v>0</v>
+      </c>
+      <c r="H18" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="52">
+        <v>32319</v>
+      </c>
+      <c r="F19" s="53">
+        <v>20602</v>
+      </c>
+      <c r="G19" s="54">
+        <v>0</v>
+      </c>
+      <c r="H19" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="52">
+        <v>32319</v>
+      </c>
+      <c r="F20" s="53">
+        <v>9955</v>
+      </c>
+      <c r="G20" s="54">
+        <v>0</v>
+      </c>
+      <c r="H20" s="53">
+        <v>9955</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="52">
+        <v>32319</v>
+      </c>
+      <c r="F21" s="53">
+        <v>3719</v>
+      </c>
+      <c r="G21" s="54">
+        <v>0</v>
+      </c>
+      <c r="H21" s="53">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="52">
+        <v>32325</v>
+      </c>
+      <c r="F22" s="53">
+        <v>10064.65</v>
+      </c>
+      <c r="G22" s="54">
+        <v>0</v>
+      </c>
+      <c r="H22" s="53">
+        <v>10064.65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="52">
+        <v>32326</v>
+      </c>
+      <c r="F23" s="53">
+        <v>4674</v>
+      </c>
+      <c r="G23" s="54">
+        <v>0</v>
+      </c>
+      <c r="H23" s="53">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="52">
+        <v>32327</v>
+      </c>
+      <c r="F24" s="53">
+        <v>6897</v>
+      </c>
+      <c r="G24" s="54">
+        <v>0</v>
+      </c>
+      <c r="H24" s="53">
+        <v>6897</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="52">
+        <v>32328</v>
+      </c>
+      <c r="F25" s="53">
+        <v>930</v>
+      </c>
+      <c r="G25" s="54">
+        <v>0</v>
+      </c>
+      <c r="H25" s="53">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="52">
+        <v>32332</v>
+      </c>
+      <c r="F26" s="53">
+        <v>2920</v>
+      </c>
+      <c r="G26" s="54">
+        <v>0</v>
+      </c>
+      <c r="H26" s="53">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="52">
+        <v>32332</v>
+      </c>
+      <c r="F27" s="53">
+        <v>25210</v>
+      </c>
+      <c r="G27" s="54">
+        <v>0</v>
+      </c>
+      <c r="H27" s="53">
+        <v>25210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="52">
+        <v>32332</v>
+      </c>
+      <c r="F28" s="53">
+        <v>343.8</v>
+      </c>
+      <c r="G28" s="54">
+        <v>0</v>
+      </c>
+      <c r="H28" s="53">
+        <v>343.8</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="52">
+        <v>32343</v>
+      </c>
+      <c r="F29" s="53">
+        <v>20108</v>
+      </c>
+      <c r="G29" s="54">
+        <v>0</v>
+      </c>
+      <c r="H29" s="53">
+        <v>20108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="52">
+        <v>32350</v>
+      </c>
+      <c r="F30" s="53">
+        <v>559.6</v>
+      </c>
+      <c r="G30" s="54">
+        <v>0</v>
+      </c>
+      <c r="H30" s="53">
+        <v>559.6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="52">
+        <v>32356</v>
+      </c>
+      <c r="F31" s="53">
+        <v>12685</v>
+      </c>
+      <c r="G31" s="54">
+        <v>0</v>
+      </c>
+      <c r="H31" s="53">
+        <v>12685</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="52">
+        <v>32356</v>
+      </c>
+      <c r="F32" s="53">
+        <v>775</v>
+      </c>
+      <c r="G32" s="54">
+        <v>0</v>
+      </c>
+      <c r="H32" s="53">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="52">
+        <v>32357</v>
+      </c>
+      <c r="F33" s="53">
+        <v>1238</v>
+      </c>
+      <c r="G33" s="54">
+        <v>0</v>
+      </c>
+      <c r="H33" s="53">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="52">
+        <v>32369</v>
+      </c>
+      <c r="F34" s="53">
+        <v>18532</v>
+      </c>
+      <c r="G34" s="54">
+        <v>0</v>
+      </c>
+      <c r="H34" s="53">
+        <v>18532</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="52">
+        <v>32372</v>
+      </c>
+      <c r="F35" s="53">
+        <v>560</v>
+      </c>
+      <c r="G35" s="54">
+        <v>0</v>
+      </c>
+      <c r="H35" s="53">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="52">
+        <v>32381</v>
+      </c>
+      <c r="F36" s="53">
+        <v>4110</v>
+      </c>
+      <c r="G36" s="54">
+        <v>0</v>
+      </c>
+      <c r="H36" s="53">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="52">
+        <v>32382</v>
+      </c>
+      <c r="F37" s="53">
+        <v>3117</v>
+      </c>
+      <c r="G37" s="54">
+        <v>0</v>
+      </c>
+      <c r="H37" s="53">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="52">
+        <v>32382</v>
+      </c>
+      <c r="F38" s="53">
+        <v>10152</v>
+      </c>
+      <c r="G38" s="54">
+        <v>0</v>
+      </c>
+      <c r="H38" s="53">
+        <v>10152</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="52">
+        <v>32387</v>
+      </c>
+      <c r="F39" s="53">
+        <v>536.79999999999995</v>
+      </c>
+      <c r="G39" s="54">
+        <v>0</v>
+      </c>
+      <c r="H39" s="53">
+        <v>536.79999999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="52">
+        <v>32391</v>
+      </c>
+      <c r="F40" s="53">
+        <v>3632</v>
+      </c>
+      <c r="G40" s="54">
+        <v>0</v>
+      </c>
+      <c r="H40" s="53">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="52">
+        <v>32403</v>
+      </c>
+      <c r="F41" s="53">
+        <v>7807</v>
+      </c>
+      <c r="G41" s="54">
+        <v>0</v>
+      </c>
+      <c r="H41" s="53">
+        <v>7807</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="52">
+        <v>32411</v>
+      </c>
+      <c r="F42" s="53">
+        <v>971.7</v>
+      </c>
+      <c r="G42" s="54">
+        <v>0</v>
+      </c>
+      <c r="H42" s="53">
+        <v>971.7</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="52">
+        <v>32417</v>
+      </c>
+      <c r="F43" s="53">
+        <v>12455</v>
+      </c>
+      <c r="G43" s="54">
+        <v>0</v>
+      </c>
+      <c r="H43" s="53">
+        <v>12455</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="52">
+        <v>32425</v>
+      </c>
+      <c r="F44" s="53">
+        <v>64050</v>
+      </c>
+      <c r="G44" s="54">
+        <v>0</v>
+      </c>
+      <c r="H44" s="53">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="52">
+        <v>32433</v>
+      </c>
+      <c r="F45" s="53">
+        <v>787.8</v>
+      </c>
+      <c r="G45" s="54">
+        <v>0</v>
+      </c>
+      <c r="H45" s="53">
+        <v>787.8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="52">
+        <v>32460</v>
+      </c>
+      <c r="F46" s="53">
+        <v>766.8</v>
+      </c>
+      <c r="G46" s="54">
+        <v>0</v>
+      </c>
+      <c r="H46" s="53">
+        <v>766.8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="52">
+        <v>32475</v>
+      </c>
+      <c r="F47" s="53">
+        <v>15365</v>
+      </c>
+      <c r="G47" s="54">
+        <v>0</v>
+      </c>
+      <c r="H47" s="53">
+        <v>15365</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="52">
+        <v>32480</v>
+      </c>
+      <c r="F48" s="53">
+        <v>7346</v>
+      </c>
+      <c r="G48" s="54">
+        <v>0</v>
+      </c>
+      <c r="H48" s="53">
+        <v>7346</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="52">
+        <v>32491</v>
+      </c>
+      <c r="F49" s="53">
+        <v>1809.85</v>
+      </c>
+      <c r="G49" s="54">
+        <v>0</v>
+      </c>
+      <c r="H49" s="53">
+        <v>1809.85</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="52">
+        <v>32502</v>
+      </c>
+      <c r="F50" s="53">
+        <v>6287.85</v>
+      </c>
+      <c r="G50" s="54">
+        <v>0</v>
+      </c>
+      <c r="H50" s="53">
+        <v>6287.85</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="52">
+        <v>32513</v>
+      </c>
+      <c r="F51" s="53">
+        <v>325</v>
+      </c>
+      <c r="G51" s="54">
+        <v>0</v>
+      </c>
+      <c r="H51" s="53">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="52">
+        <v>32515</v>
+      </c>
+      <c r="F52" s="53">
+        <v>16788</v>
+      </c>
+      <c r="G52" s="54">
+        <v>0</v>
+      </c>
+      <c r="H52" s="53">
+        <v>16788</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="52">
+        <v>32524</v>
+      </c>
+      <c r="F53" s="53">
+        <v>24650</v>
+      </c>
+      <c r="G53" s="54">
+        <v>0</v>
+      </c>
+      <c r="H53" s="53">
+        <v>24650</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" s="52">
+        <v>32540</v>
+      </c>
+      <c r="F54" s="53">
+        <v>14188</v>
+      </c>
+      <c r="G54" s="54">
+        <v>0</v>
+      </c>
+      <c r="H54" s="53">
+        <v>14188</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" s="52">
+        <v>32544</v>
+      </c>
+      <c r="F55" s="53">
+        <v>23406</v>
+      </c>
+      <c r="G55" s="54">
+        <v>0</v>
+      </c>
+      <c r="H55" s="53">
+        <v>23406</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="52">
+        <v>32548</v>
+      </c>
+      <c r="F56" s="53">
+        <v>19293.7</v>
+      </c>
+      <c r="G56" s="54">
+        <v>0</v>
+      </c>
+      <c r="H56" s="53">
+        <v>19293.7</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" s="52">
+        <v>32558</v>
+      </c>
+      <c r="F57" s="53">
+        <v>1975</v>
+      </c>
+      <c r="G57" s="54">
+        <v>0</v>
+      </c>
+      <c r="H57" s="53">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" s="52">
+        <v>32561</v>
+      </c>
+      <c r="F58" s="53">
+        <v>12736</v>
+      </c>
+      <c r="G58" s="54">
+        <v>0</v>
+      </c>
+      <c r="H58" s="53">
+        <v>12736</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E59" s="52">
+        <v>32564</v>
+      </c>
+      <c r="F59" s="53">
+        <v>2150</v>
+      </c>
+      <c r="G59" s="54">
+        <v>8.5</v>
+      </c>
+      <c r="H59" s="53">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="52">
+        <v>32568</v>
+      </c>
+      <c r="F60" s="53">
+        <v>15355</v>
+      </c>
+      <c r="G60" s="54">
+        <v>0</v>
+      </c>
+      <c r="H60" s="53">
+        <v>15355</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E61" s="52">
+        <v>32571</v>
+      </c>
+      <c r="F61" s="53">
+        <v>24277.3</v>
+      </c>
+      <c r="G61" s="54">
+        <v>0</v>
+      </c>
+      <c r="H61" s="53">
+        <v>24277.3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62" s="52">
+        <v>32576</v>
+      </c>
+      <c r="F62" s="53">
+        <v>18320</v>
+      </c>
+      <c r="G62" s="54">
+        <v>0</v>
+      </c>
+      <c r="H62" s="53">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="B63" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="52">
+        <v>32581</v>
+      </c>
+      <c r="F63" s="53">
+        <v>61869.3</v>
+      </c>
+      <c r="G63" s="54">
+        <v>0</v>
+      </c>
+      <c r="H63" s="53">
+        <v>61869.3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="52">
+        <v>32592</v>
+      </c>
+      <c r="F64" s="53">
+        <v>395</v>
+      </c>
+      <c r="G64" s="54">
+        <v>0</v>
+      </c>
+      <c r="H64" s="53">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="52">
+        <v>32593</v>
+      </c>
+      <c r="F65" s="53">
+        <v>17814</v>
+      </c>
+      <c r="G65" s="54">
+        <v>0</v>
+      </c>
+      <c r="H65" s="53">
+        <v>17814</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" s="52">
+        <v>32594</v>
+      </c>
+      <c r="F66" s="53">
+        <v>19812</v>
+      </c>
+      <c r="G66" s="54">
+        <v>0</v>
+      </c>
+      <c r="H66" s="53">
+        <v>19812</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E67" s="52">
+        <v>32600</v>
+      </c>
+      <c r="F67" s="53">
+        <v>4495</v>
+      </c>
+      <c r="G67" s="54">
+        <v>0</v>
+      </c>
+      <c r="H67" s="53">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="B68" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C68" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E68" s="52">
+        <v>32602</v>
+      </c>
+      <c r="F68" s="53">
+        <v>31847</v>
+      </c>
+      <c r="G68" s="54">
+        <v>0</v>
+      </c>
+      <c r="H68" s="53">
+        <v>31847</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E69" s="52">
+        <v>32604</v>
+      </c>
+      <c r="F69" s="53">
+        <v>33829.449999999997</v>
+      </c>
+      <c r="G69" s="54">
+        <v>0</v>
+      </c>
+      <c r="H69" s="53">
+        <v>33829.449999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8">
+      <c r="B70" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="E70" s="52">
+        <v>32606</v>
+      </c>
+      <c r="F70" s="53">
+        <v>22354</v>
+      </c>
+      <c r="G70" s="54">
+        <v>0</v>
+      </c>
+      <c r="H70" s="53">
+        <v>22354</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8">
+      <c r="B71" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="E71" s="52">
+        <v>32608</v>
+      </c>
+      <c r="F71" s="53">
+        <v>103041</v>
+      </c>
+      <c r="G71" s="54">
+        <v>0</v>
+      </c>
+      <c r="H71" s="53">
+        <v>103041</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8">
+      <c r="B72" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" s="52">
+        <v>32610</v>
+      </c>
+      <c r="F72" s="53">
+        <v>3596</v>
+      </c>
+      <c r="G72" s="54">
+        <v>0</v>
+      </c>
+      <c r="H72" s="53">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="B73" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C73" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" s="52">
+        <v>32614</v>
+      </c>
+      <c r="F73" s="53">
+        <v>19414</v>
+      </c>
+      <c r="G73" s="54">
+        <v>0</v>
+      </c>
+      <c r="H73" s="53">
+        <v>19414</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" s="52">
+        <v>32618</v>
+      </c>
+      <c r="F74" s="53">
+        <v>2195</v>
+      </c>
+      <c r="G74" s="54">
+        <v>0</v>
+      </c>
+      <c r="H74" s="53">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8">
+      <c r="B75" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D75" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="E75" s="52">
+        <v>32620</v>
+      </c>
+      <c r="F75" s="53">
+        <v>8560</v>
+      </c>
+      <c r="G75" s="54">
+        <v>0</v>
+      </c>
+      <c r="H75" s="53">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="B76" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76" s="52">
+        <v>32624</v>
+      </c>
+      <c r="F76" s="53">
+        <v>17781</v>
+      </c>
+      <c r="G76" s="54">
+        <v>0</v>
+      </c>
+      <c r="H76" s="53">
+        <v>17781</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E77" s="52">
+        <v>32629</v>
+      </c>
+      <c r="F77" s="53">
+        <v>156</v>
+      </c>
+      <c r="G77" s="54">
+        <v>0</v>
+      </c>
+      <c r="H77" s="53">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="E78" s="52">
+        <v>32630</v>
+      </c>
+      <c r="F78" s="53">
+        <v>79116</v>
+      </c>
+      <c r="G78" s="54">
+        <v>0</v>
+      </c>
+      <c r="H78" s="53">
+        <v>79116</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="E79" s="52">
+        <v>32632</v>
+      </c>
+      <c r="F79" s="53">
+        <v>4445</v>
+      </c>
+      <c r="G79" s="54">
+        <v>0</v>
+      </c>
+      <c r="H79" s="53">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E80" s="52">
+        <v>32634</v>
+      </c>
+      <c r="F80" s="53">
+        <v>9634</v>
+      </c>
+      <c r="G80" s="54">
+        <v>0</v>
+      </c>
+      <c r="H80" s="53">
+        <v>9634</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D81" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="E81" s="52">
+        <v>32636</v>
+      </c>
+      <c r="F81" s="53">
+        <v>30566</v>
+      </c>
+      <c r="G81" s="54">
+        <v>0</v>
+      </c>
+      <c r="H81" s="53">
+        <v>30566</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
+      <c r="B82" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D82" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="52">
+        <v>32638</v>
+      </c>
+      <c r="F82" s="53">
+        <v>1416.45</v>
+      </c>
+      <c r="G82" s="54">
+        <v>0</v>
+      </c>
+      <c r="H82" s="53">
+        <v>1416.45</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8">
+      <c r="B83" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C83" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D83" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" s="52">
+        <v>32638</v>
+      </c>
+      <c r="F83" s="53">
+        <v>11164.8</v>
+      </c>
+      <c r="G83" s="54">
+        <v>0</v>
+      </c>
+      <c r="H83" s="53">
+        <v>11164.8</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
+      <c r="B84" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84" s="52">
+        <v>32640</v>
+      </c>
+      <c r="F84" s="53">
+        <v>1185</v>
+      </c>
+      <c r="G84" s="54">
+        <v>0</v>
+      </c>
+      <c r="H84" s="53">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8">
+      <c r="B85" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" s="52">
+        <v>32647</v>
+      </c>
+      <c r="F85" s="53">
+        <v>14049.95</v>
+      </c>
+      <c r="G85" s="54">
+        <v>0</v>
+      </c>
+      <c r="H85" s="53">
+        <v>14049.95</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
+      <c r="B86" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E86" s="52">
+        <v>32649</v>
+      </c>
+      <c r="F86" s="53">
+        <v>14045</v>
+      </c>
+      <c r="G86" s="54">
+        <v>0</v>
+      </c>
+      <c r="H86" s="53">
+        <v>14045</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8">
+      <c r="B87" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E87" s="52">
+        <v>32651</v>
+      </c>
+      <c r="F87" s="53">
+        <v>2706</v>
+      </c>
+      <c r="G87" s="54">
+        <v>0</v>
+      </c>
+      <c r="H87" s="53">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
+      <c r="B88" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="E88" s="52">
+        <v>32654</v>
+      </c>
+      <c r="F88" s="53">
+        <v>8507</v>
+      </c>
+      <c r="G88" s="54">
+        <v>0</v>
+      </c>
+      <c r="H88" s="53">
+        <v>8507</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8">
+      <c r="B89" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E89" s="52">
+        <v>32660</v>
+      </c>
+      <c r="F89" s="53">
+        <v>1950</v>
+      </c>
+      <c r="G89" s="54">
+        <v>0</v>
+      </c>
+      <c r="H89" s="53">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
+      <c r="B90" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C90" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E90" s="52">
+        <v>32660</v>
+      </c>
+      <c r="F90" s="53">
+        <v>76698.75</v>
+      </c>
+      <c r="G90" s="54">
+        <v>0</v>
+      </c>
+      <c r="H90" s="53">
+        <v>76698.75</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
+      <c r="B91" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C91" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E91" s="52">
+        <v>32661</v>
+      </c>
+      <c r="F91" s="53">
+        <v>479.8</v>
+      </c>
+      <c r="G91" s="54">
+        <v>0</v>
+      </c>
+      <c r="H91" s="53">
+        <v>479.8</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8">
+      <c r="B92" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C92" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E92" s="52">
+        <v>32663</v>
+      </c>
+      <c r="F92" s="53">
+        <v>4113.75</v>
+      </c>
+      <c r="G92" s="54">
+        <v>0</v>
+      </c>
+      <c r="H92" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8">
+      <c r="B93" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" s="52">
+        <v>32665</v>
+      </c>
+      <c r="F93" s="53">
+        <v>7531.75</v>
+      </c>
+      <c r="G93" s="54">
+        <v>0</v>
+      </c>
+      <c r="H93" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
+      <c r="B94" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C94" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" s="52">
+        <v>32668</v>
+      </c>
+      <c r="F94" s="53">
+        <v>123740</v>
+      </c>
+      <c r="G94" s="54">
+        <v>0</v>
+      </c>
+      <c r="H94" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8">
+      <c r="B95" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="E95" s="52">
+        <v>32671</v>
+      </c>
+      <c r="F95" s="53">
+        <v>12953.6</v>
+      </c>
+      <c r="G95" s="54">
+        <v>0</v>
+      </c>
+      <c r="H95" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
+      <c r="B96" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="E96" s="52">
+        <v>32673</v>
+      </c>
+      <c r="F96" s="53">
+        <v>472.9</v>
+      </c>
+      <c r="G96" s="54">
+        <v>0</v>
+      </c>
+      <c r="H96" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8">
+      <c r="B97" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E97" s="52">
+        <v>32675</v>
+      </c>
+      <c r="F97" s="53">
+        <v>859.95</v>
+      </c>
+      <c r="G97" s="54">
+        <v>0</v>
+      </c>
+      <c r="H97" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8">
+      <c r="B98" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="E98" s="52">
+        <v>32679</v>
+      </c>
+      <c r="F98" s="53">
+        <v>6094.8</v>
+      </c>
+      <c r="G98" s="54">
+        <v>0</v>
+      </c>
+      <c r="H98" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8">
+      <c r="B99" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="E99" s="52">
+        <v>32693</v>
+      </c>
+      <c r="F99" s="53">
+        <v>11629.85</v>
+      </c>
+      <c r="G99" s="54">
+        <v>0</v>
+      </c>
+      <c r="H99" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="E100" s="52">
+        <v>33761</v>
+      </c>
+      <c r="F100" s="53">
+        <v>2844</v>
+      </c>
+      <c r="G100" s="54">
+        <v>0</v>
+      </c>
+      <c r="H100" s="53">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8">
+      <c r="B101" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C101" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="E101" s="52">
+        <v>33798</v>
+      </c>
+      <c r="F101" s="53">
+        <v>39797.699999999997</v>
+      </c>
+      <c r="G101" s="54">
+        <v>0</v>
+      </c>
+      <c r="H101" s="53">
+        <v>39797.699999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="C102" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E102" s="52">
+        <v>33803</v>
+      </c>
+      <c r="F102" s="53">
+        <v>51673.15</v>
+      </c>
+      <c r="G102" s="54">
+        <v>0</v>
+      </c>
+      <c r="H102" s="53">
+        <v>51673.15</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" s="52">
+        <v>33806</v>
+      </c>
+      <c r="F103" s="53">
+        <v>31219.95</v>
+      </c>
+      <c r="G103" s="54">
+        <v>0</v>
+      </c>
+      <c r="H103" s="53">
+        <v>31219.95</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="E104" s="52">
+        <v>33870</v>
+      </c>
+      <c r="F104" s="53">
+        <v>3531.8</v>
+      </c>
+      <c r="G104" s="54">
+        <v>0</v>
+      </c>
+      <c r="H104" s="53">
+        <v>3531.8</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8">
+      <c r="B105" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="E105" s="52">
+        <v>33901</v>
+      </c>
+      <c r="F105" s="53">
+        <v>28389</v>
+      </c>
+      <c r="G105" s="54">
+        <v>0</v>
+      </c>
+      <c r="H105" s="53">
+        <v>28389</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C106" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D106" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="E106" s="52">
+        <v>33921</v>
+      </c>
+      <c r="F106" s="53">
+        <v>203</v>
+      </c>
+      <c r="G106" s="54">
+        <v>0</v>
+      </c>
+      <c r="H106" s="53">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8">
+      <c r="B107" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="E107" s="52">
+        <v>33952</v>
+      </c>
+      <c r="F107" s="53">
+        <v>4720.8</v>
+      </c>
+      <c r="G107" s="54">
+        <v>0</v>
+      </c>
+      <c r="H107" s="53">
+        <v>4720.8</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8">
+      <c r="B108" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C108" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E108" s="52">
+        <v>33971</v>
+      </c>
+      <c r="F108" s="53">
+        <v>5565</v>
+      </c>
+      <c r="G108" s="54">
+        <v>0</v>
+      </c>
+      <c r="H108" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8">
+      <c r="B109" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C109" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="E109" s="52">
+        <v>34012</v>
+      </c>
+      <c r="F109" s="53">
+        <v>2514.65</v>
+      </c>
+      <c r="G109" s="54">
+        <v>0</v>
+      </c>
+      <c r="H109" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8">
+      <c r="B110" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D110" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="E110" s="52">
+        <v>34041</v>
+      </c>
+      <c r="F110" s="53">
+        <v>4894.95</v>
+      </c>
+      <c r="G110" s="54">
+        <v>0</v>
+      </c>
+      <c r="H110" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8">
+      <c r="B111" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C111" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E111" s="52">
+        <v>34049</v>
+      </c>
+      <c r="F111" s="53">
+        <v>23104</v>
+      </c>
+      <c r="G111" s="54">
+        <v>0</v>
+      </c>
+      <c r="H111" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8">
+      <c r="B112" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E112" s="52">
+        <v>34072</v>
+      </c>
+      <c r="F112" s="53">
+        <v>6734.85</v>
+      </c>
+      <c r="G112" s="54">
+        <v>0</v>
+      </c>
+      <c r="H112" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8">
+      <c r="B113" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E113" s="52">
+        <v>34082</v>
+      </c>
+      <c r="F113" s="53">
+        <v>21614</v>
+      </c>
+      <c r="G113" s="54">
+        <v>0</v>
+      </c>
+      <c r="H113" s="53">
+        <v>21614</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8">
+      <c r="B114" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C114" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="E114" s="52">
+        <v>34104</v>
+      </c>
+      <c r="F114" s="53">
+        <v>14557.95</v>
+      </c>
+      <c r="G114" s="54">
+        <v>0</v>
+      </c>
+      <c r="H114" s="53">
+        <v>14557.95</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8">
+      <c r="B115" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E115" s="52">
+        <v>34114</v>
+      </c>
+      <c r="F115" s="53">
+        <v>784.9</v>
+      </c>
+      <c r="G115" s="54">
+        <v>0</v>
+      </c>
+      <c r="H115" s="53">
+        <v>784.9</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8">
+      <c r="B116" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="E116" s="52">
+        <v>34122</v>
+      </c>
+      <c r="F116" s="53">
+        <v>820</v>
+      </c>
+      <c r="G116" s="54">
+        <v>0</v>
+      </c>
+      <c r="H116" s="53">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8">
+      <c r="B117" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" s="52">
+        <v>34173</v>
+      </c>
+      <c r="F117" s="53">
+        <v>44854</v>
+      </c>
+      <c r="G117" s="54">
+        <v>0</v>
+      </c>
+      <c r="H117" s="53">
+        <v>44854</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8">
+      <c r="B118" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C118" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="E118" s="52">
+        <v>34205</v>
+      </c>
+      <c r="F118" s="53">
+        <v>13945</v>
+      </c>
+      <c r="G118" s="54">
+        <v>0</v>
+      </c>
+      <c r="H118" s="53">
+        <v>13945</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8">
+      <c r="B119" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E119" s="52">
+        <v>34213</v>
+      </c>
+      <c r="F119" s="53">
+        <v>33071</v>
+      </c>
+      <c r="G119" s="54">
+        <v>0</v>
+      </c>
+      <c r="H119" s="53">
+        <v>33071</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8">
+      <c r="B120" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C120" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D120" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="E120" s="52">
+        <v>34216</v>
+      </c>
+      <c r="F120" s="53">
+        <v>6583.8</v>
+      </c>
+      <c r="G120" s="54">
+        <v>0</v>
+      </c>
+      <c r="H120" s="53">
+        <v>6583.8</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8">
+      <c r="B121" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C121" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D121" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E121" s="52">
+        <v>34243</v>
+      </c>
+      <c r="F121" s="53">
+        <v>10107</v>
+      </c>
+      <c r="G121" s="54">
+        <v>0</v>
+      </c>
+      <c r="H121" s="53">
+        <v>10107</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8">
+      <c r="B122" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D122" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E122" s="52">
+        <v>34244</v>
+      </c>
+      <c r="F122" s="53">
+        <v>25071</v>
+      </c>
+      <c r="G122" s="54">
+        <v>0</v>
+      </c>
+      <c r="H122" s="53">
+        <v>25071</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8">
+      <c r="B123" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C123" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" s="52">
+        <v>34250</v>
+      </c>
+      <c r="F123" s="53">
+        <v>8294</v>
+      </c>
+      <c r="G123" s="54">
+        <v>0</v>
+      </c>
+      <c r="H123" s="53">
+        <v>8294</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8">
+      <c r="B124" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C124" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D124" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E124" s="52">
+        <v>34261</v>
+      </c>
+      <c r="F124" s="53">
+        <v>1004.8</v>
+      </c>
+      <c r="G124" s="54">
+        <v>0</v>
+      </c>
+      <c r="H124" s="53">
+        <v>1004.8</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8">
+      <c r="B125" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="C125" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D125" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="E125" s="52">
+        <v>34268</v>
+      </c>
+      <c r="F125" s="53">
+        <v>6300</v>
+      </c>
+      <c r="G125" s="54">
+        <v>0</v>
+      </c>
+      <c r="H125" s="53">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8">
+      <c r="B126" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="E126" s="52">
+        <v>34274</v>
+      </c>
+      <c r="F126" s="53">
+        <v>11989.2</v>
+      </c>
+      <c r="G126" s="54">
+        <v>0</v>
+      </c>
+      <c r="H126" s="53">
+        <v>11989.2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8">
+      <c r="B127" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C127" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="E127" s="52">
+        <v>34274</v>
+      </c>
+      <c r="F127" s="53">
+        <v>906</v>
+      </c>
+      <c r="G127" s="54">
+        <v>0</v>
+      </c>
+      <c r="H127" s="53">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8">
+      <c r="B128" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C128" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D128" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="E128" s="52">
+        <v>34275</v>
+      </c>
+      <c r="F128" s="53">
+        <v>2419</v>
+      </c>
+      <c r="G128" s="54">
+        <v>0</v>
+      </c>
+      <c r="H128" s="53">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8">
+      <c r="B129" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="C129" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D129" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E129" s="52">
+        <v>34287</v>
+      </c>
+      <c r="F129" s="53">
+        <v>6675.95</v>
+      </c>
+      <c r="G129" s="54">
+        <v>0</v>
+      </c>
+      <c r="H129" s="53">
+        <v>6675.95</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8">
+      <c r="B130" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C130" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E130" s="52">
+        <v>34300</v>
+      </c>
+      <c r="F130" s="53">
+        <v>2971</v>
+      </c>
+      <c r="G130" s="54">
+        <v>0</v>
+      </c>
+      <c r="H130" s="53">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8">
+      <c r="B131" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C131" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E131" s="52">
+        <v>34300</v>
+      </c>
+      <c r="F131" s="53">
+        <v>6785.4</v>
+      </c>
+      <c r="G131" s="54">
+        <v>0</v>
+      </c>
+      <c r="H131" s="53">
+        <v>6785.4</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8">
+      <c r="B132" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C132" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D132" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132" s="52">
+        <v>34304</v>
+      </c>
+      <c r="F132" s="53">
+        <v>47710.75</v>
+      </c>
+      <c r="G132" s="54">
+        <v>0</v>
+      </c>
+      <c r="H132" s="53">
+        <v>47710.75</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8">
+      <c r="B133" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D133" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="E133" s="52">
+        <v>34315</v>
+      </c>
+      <c r="F133" s="53">
+        <v>1240</v>
+      </c>
+      <c r="G133" s="54">
+        <v>0</v>
+      </c>
+      <c r="H133" s="53">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8">
+      <c r="B134" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C134" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D134" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134" s="52">
+        <v>34320</v>
+      </c>
+      <c r="F134" s="53">
+        <v>1846</v>
+      </c>
+      <c r="G134" s="54">
+        <v>0</v>
+      </c>
+      <c r="H134" s="53">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8">
+      <c r="B135" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C135" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D135" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E135" s="52">
+        <v>34328</v>
+      </c>
+      <c r="F135" s="53">
+        <v>3546</v>
+      </c>
+      <c r="G135" s="54">
+        <v>0</v>
+      </c>
+      <c r="H135" s="53">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
+      <c r="B136" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C136" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="E136" s="52">
+        <v>34335</v>
+      </c>
+      <c r="F136" s="53">
+        <v>3087</v>
+      </c>
+      <c r="G136" s="54">
+        <v>0</v>
+      </c>
+      <c r="H136" s="53">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8">
+      <c r="B137" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C137" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E137" s="52">
+        <v>34343</v>
+      </c>
+      <c r="F137" s="53">
+        <v>10054</v>
+      </c>
+      <c r="G137" s="54">
+        <v>0</v>
+      </c>
+      <c r="H137" s="53">
+        <v>10054</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8">
+      <c r="B138" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C138" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="E138" s="52">
+        <v>34351</v>
+      </c>
+      <c r="F138" s="53">
+        <v>4229.8</v>
+      </c>
+      <c r="G138" s="54">
+        <v>0</v>
+      </c>
+      <c r="H138" s="53">
+        <v>4229.8</v>
+      </c>
+    </row>
+    <row r="139" spans="2:8">
+      <c r="B139" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C139" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D139" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E139" s="52">
+        <v>34378</v>
+      </c>
+      <c r="F139" s="53">
+        <v>15052</v>
+      </c>
+      <c r="G139" s="54">
+        <v>0</v>
+      </c>
+      <c r="H139" s="53">
+        <v>15052</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8">
+      <c r="B140" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C140" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D140" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="E140" s="52">
+        <v>34396</v>
+      </c>
+      <c r="F140" s="53">
+        <v>5011</v>
+      </c>
+      <c r="G140" s="54">
+        <v>0</v>
+      </c>
+      <c r="H140" s="53">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8">
+      <c r="B141" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C141" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D141" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="E141" s="52">
+        <v>34407</v>
+      </c>
+      <c r="F141" s="53">
+        <v>12900.75</v>
+      </c>
+      <c r="G141" s="54">
+        <v>0</v>
+      </c>
+      <c r="H141" s="53">
+        <v>12900.75</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8">
+      <c r="B142" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D142" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="E142" s="52">
+        <v>34418</v>
+      </c>
+      <c r="F142" s="53">
+        <v>7671.9</v>
+      </c>
+      <c r="G142" s="54">
+        <v>0</v>
+      </c>
+      <c r="H142" s="53">
+        <v>7671.9</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8">
+      <c r="B143" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="E143" s="52">
+        <v>34431</v>
+      </c>
+      <c r="F143" s="53">
+        <v>97698.6</v>
+      </c>
+      <c r="G143" s="54">
+        <v>0</v>
+      </c>
+      <c r="H143" s="53">
+        <v>97698.6</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8">
+      <c r="B144" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="E144" s="52">
+        <v>34440</v>
+      </c>
+      <c r="F144" s="53">
+        <v>3860.85</v>
+      </c>
+      <c r="G144" s="54">
+        <v>0</v>
+      </c>
+      <c r="H144" s="53">
+        <v>3860.85</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8">
+      <c r="B145" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C145" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="E145" s="52">
+        <v>34455</v>
+      </c>
+      <c r="F145" s="53">
+        <v>13226.8</v>
+      </c>
+      <c r="G145" s="54">
+        <v>0</v>
+      </c>
+      <c r="H145" s="53">
+        <v>13226.8</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8">
+      <c r="B146" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E146" s="52">
+        <v>34459</v>
+      </c>
+      <c r="F146" s="53">
+        <v>13935.95</v>
+      </c>
+      <c r="G146" s="54">
+        <v>0</v>
+      </c>
+      <c r="H146" s="53">
+        <v>13935.95</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8">
+      <c r="B147" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C147" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D147" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="E147" s="52">
+        <v>34463</v>
+      </c>
+      <c r="F147" s="53">
+        <v>12367</v>
+      </c>
+      <c r="G147" s="54">
+        <v>0</v>
+      </c>
+      <c r="H147" s="53">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8">
+      <c r="B148" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C148" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E148" s="52">
+        <v>34476</v>
+      </c>
+      <c r="F148" s="53">
+        <v>9793.5499999999993</v>
+      </c>
+      <c r="G148" s="54">
+        <v>0</v>
+      </c>
+      <c r="H148" s="53">
+        <v>9793.5499999999993</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8">
+      <c r="B149" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C149" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D149" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E149" s="52">
+        <v>34486</v>
+      </c>
+      <c r="F149" s="53">
+        <v>2206.85</v>
+      </c>
+      <c r="G149" s="54">
+        <v>0</v>
+      </c>
+      <c r="H149" s="53">
+        <v>2206.85</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8">
+      <c r="B150" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C150" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="51" t="s">
+        <v>224</v>
+      </c>
+      <c r="E150" s="52">
+        <v>34489</v>
+      </c>
+      <c r="F150" s="53">
+        <v>102453.6</v>
+      </c>
+      <c r="G150" s="54">
+        <v>0</v>
+      </c>
+      <c r="H150" s="53">
+        <v>102453.6</v>
+      </c>
+    </row>
+    <row r="151" spans="2:8">
+      <c r="B151" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C151" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E151" s="52">
+        <v>34494</v>
+      </c>
+      <c r="F151" s="53">
+        <v>3153</v>
+      </c>
+      <c r="G151" s="54">
+        <v>0</v>
+      </c>
+      <c r="H151" s="53">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="152" spans="2:8">
+      <c r="B152" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="E152" s="52">
+        <v>34499</v>
+      </c>
+      <c r="F152" s="53">
+        <v>342</v>
+      </c>
+      <c r="G152" s="54">
+        <v>0</v>
+      </c>
+      <c r="H152" s="53">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="153" spans="2:8">
+      <c r="B153" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C153" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="E153" s="52">
+        <v>34511</v>
+      </c>
+      <c r="F153" s="53">
+        <v>2692.85</v>
+      </c>
+      <c r="G153" s="54">
+        <v>0</v>
+      </c>
+      <c r="H153" s="53">
+        <v>2692.85</v>
+      </c>
+    </row>
+    <row r="154" spans="2:8">
+      <c r="B154" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C154" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D154" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="E154" s="52">
+        <v>34516</v>
+      </c>
+      <c r="F154" s="53">
+        <v>28862</v>
+      </c>
+      <c r="G154" s="54">
+        <v>0</v>
+      </c>
+      <c r="H154" s="53">
+        <v>28862</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8">
+      <c r="B155" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C155" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D155" s="51" t="s">
+        <v>229</v>
+      </c>
+      <c r="E155" s="52">
+        <v>34519</v>
+      </c>
+      <c r="F155" s="53">
+        <v>104</v>
+      </c>
+      <c r="G155" s="54">
+        <v>0</v>
+      </c>
+      <c r="H155" s="53">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8">
+      <c r="B156" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C156" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="E156" s="52">
+        <v>34521</v>
+      </c>
+      <c r="F156" s="53">
+        <v>9471.9500000000007</v>
+      </c>
+      <c r="G156" s="54">
+        <v>0</v>
+      </c>
+      <c r="H156" s="53">
+        <v>9471.9500000000007</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8">
+      <c r="B157" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C157" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="E157" s="52">
+        <v>34523</v>
+      </c>
+      <c r="F157" s="53">
+        <v>5654.8</v>
+      </c>
+      <c r="G157" s="54">
+        <v>0</v>
+      </c>
+      <c r="H157" s="53">
+        <v>5654.8</v>
+      </c>
+    </row>
+    <row r="158" spans="2:8">
+      <c r="B158" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C158" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D158" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="E158" s="52">
+        <v>34525</v>
+      </c>
+      <c r="F158" s="53">
+        <v>2356.9</v>
+      </c>
+      <c r="G158" s="54">
+        <v>0</v>
+      </c>
+      <c r="H158" s="53">
+        <v>2356.9</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8">
+      <c r="B159" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C159" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D159" s="51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E159" s="52">
+        <v>34531</v>
+      </c>
+      <c r="F159" s="53">
+        <v>54</v>
+      </c>
+      <c r="G159" s="54">
+        <v>0</v>
+      </c>
+      <c r="H159" s="53">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8">
+      <c r="B160" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="C160" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D160" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="E160" s="52">
+        <v>34537</v>
+      </c>
+      <c r="F160" s="53">
+        <v>13814.05</v>
+      </c>
+      <c r="G160" s="54">
+        <v>0</v>
+      </c>
+      <c r="H160" s="53">
+        <v>13814.05</v>
+      </c>
+    </row>
+    <row r="161" spans="2:8">
+      <c r="B161" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C161" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D161" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="E161" s="52">
+        <v>34541</v>
+      </c>
+      <c r="F161" s="53">
+        <v>4178.8500000000004</v>
+      </c>
+      <c r="G161" s="54">
+        <v>0</v>
+      </c>
+      <c r="H161" s="53">
+        <v>4178.8500000000004</v>
+      </c>
+    </row>
+    <row r="162" spans="2:8">
+      <c r="B162" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C162" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E162" s="52">
+        <v>34548</v>
+      </c>
+      <c r="F162" s="53">
+        <v>5511.75</v>
+      </c>
+      <c r="G162" s="54">
+        <v>0</v>
+      </c>
+      <c r="H162" s="53">
+        <v>5511.75</v>
+      </c>
+    </row>
+    <row r="163" spans="2:8">
+      <c r="B163" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="E163" s="52">
+        <v>34552</v>
+      </c>
+      <c r="F163" s="53">
+        <v>3640</v>
+      </c>
+      <c r="G163" s="54">
+        <v>0</v>
+      </c>
+      <c r="H163" s="53">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="164" spans="2:8">
+      <c r="B164" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C164" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D164" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="E164" s="52">
+        <v>34556</v>
+      </c>
+      <c r="F164" s="53">
+        <v>3650</v>
+      </c>
+      <c r="G164" s="54">
+        <v>0</v>
+      </c>
+      <c r="H164" s="53">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="165" spans="2:8">
+      <c r="B165" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C165" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D165" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E165" s="52">
+        <v>34583</v>
+      </c>
+      <c r="F165" s="53">
+        <v>7868</v>
+      </c>
+      <c r="G165" s="54">
+        <v>0</v>
+      </c>
+      <c r="H165" s="53">
+        <v>7868</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8">
+      <c r="B166" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C166" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D166" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E166" s="52">
+        <v>34585</v>
+      </c>
+      <c r="F166" s="53">
+        <v>5983</v>
+      </c>
+      <c r="G166" s="54">
+        <v>0</v>
+      </c>
+      <c r="H166" s="53">
+        <v>5983</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8">
+      <c r="B167" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C167" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D167" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="E167" s="52">
+        <v>34589</v>
+      </c>
+      <c r="F167" s="53">
+        <v>6731</v>
+      </c>
+      <c r="G167" s="54">
+        <v>0</v>
+      </c>
+      <c r="H167" s="53">
+        <v>6731</v>
+      </c>
+    </row>
+    <row r="168" spans="2:8">
+      <c r="B168" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C168" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="E168" s="52">
+        <v>34591</v>
+      </c>
+      <c r="F168" s="53">
+        <v>72089.899999999994</v>
+      </c>
+      <c r="G168" s="54">
+        <v>0</v>
+      </c>
+      <c r="H168" s="53">
+        <v>72089.899999999994</v>
+      </c>
+    </row>
+    <row r="169" spans="2:8">
+      <c r="B169" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C169" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D169" s="51" t="s">
+        <v>244</v>
+      </c>
+      <c r="E169" s="52">
+        <v>34593</v>
+      </c>
+      <c r="F169" s="53">
+        <v>716</v>
+      </c>
+      <c r="G169" s="54">
+        <v>0</v>
+      </c>
+      <c r="H169" s="53">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="170" spans="2:8">
+      <c r="B170" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D170" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="E170" s="52">
+        <v>34597</v>
+      </c>
+      <c r="F170" s="53">
+        <v>1827</v>
+      </c>
+      <c r="G170" s="54">
+        <v>0</v>
+      </c>
+      <c r="H170" s="53">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="171" spans="2:8">
+      <c r="B171" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="C171" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D171" s="51" t="s">
+        <v>247</v>
+      </c>
+      <c r="E171" s="52">
+        <v>34611</v>
+      </c>
+      <c r="F171" s="53">
+        <v>7990</v>
+      </c>
+      <c r="G171" s="54">
+        <v>0</v>
+      </c>
+      <c r="H171" s="53">
+        <v>7990</v>
+      </c>
+    </row>
+    <row r="172" spans="2:8">
+      <c r="B172" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C172" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D172" s="51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E172" s="52">
+        <v>34613</v>
+      </c>
+      <c r="F172" s="53">
+        <v>4205</v>
+      </c>
+      <c r="G172" s="54">
+        <v>0</v>
+      </c>
+      <c r="H172" s="53">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="173" spans="2:8">
+      <c r="B173" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C173" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D173" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="E173" s="52">
+        <v>34625</v>
+      </c>
+      <c r="F173" s="53">
+        <v>10263.75</v>
+      </c>
+      <c r="G173" s="54">
+        <v>0</v>
+      </c>
+      <c r="H173" s="53">
+        <v>10263.75</v>
+      </c>
+    </row>
+    <row r="174" spans="2:8">
+      <c r="B174" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C174" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D174" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="E174" s="52">
+        <v>34628</v>
+      </c>
+      <c r="F174" s="53">
+        <v>4029.55</v>
+      </c>
+      <c r="G174" s="54">
+        <v>0</v>
+      </c>
+      <c r="H174" s="53">
+        <v>4029.55</v>
+      </c>
+    </row>
+    <row r="175" spans="2:8">
+      <c r="B175" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="E175" s="52">
+        <v>34649</v>
+      </c>
+      <c r="F175" s="53">
+        <v>12949.7</v>
+      </c>
+      <c r="G175" s="54">
+        <v>0</v>
+      </c>
+      <c r="H175" s="53">
+        <v>12949.7</v>
+      </c>
+    </row>
+    <row r="176" spans="2:8">
+      <c r="B176" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C176" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D176" s="51" t="s">
+        <v>253</v>
+      </c>
+      <c r="E176" s="52">
+        <v>34650</v>
+      </c>
+      <c r="F176" s="53">
+        <v>20711.900000000001</v>
+      </c>
+      <c r="G176" s="54">
+        <v>0</v>
+      </c>
+      <c r="H176" s="53">
+        <v>20711.900000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="2:8">
+      <c r="B177" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C177" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D177" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="E177" s="52">
+        <v>34652</v>
+      </c>
+      <c r="F177" s="53">
+        <v>3975.75</v>
+      </c>
+      <c r="G177" s="54">
+        <v>0</v>
+      </c>
+      <c r="H177" s="53">
+        <v>3975.75</v>
+      </c>
+    </row>
+    <row r="178" spans="2:8">
+      <c r="B178" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C178" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D178" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="E178" s="52">
+        <v>34654</v>
+      </c>
+      <c r="F178" s="53">
+        <v>8305.9500000000007</v>
+      </c>
+      <c r="G178" s="54">
+        <v>0</v>
+      </c>
+      <c r="H178" s="53">
+        <v>8305.9500000000007</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8">
+      <c r="B179" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C179" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D179" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="E179" s="52">
+        <v>34660</v>
+      </c>
+      <c r="F179" s="53">
+        <v>51730.8</v>
+      </c>
+      <c r="G179" s="54">
+        <v>0</v>
+      </c>
+      <c r="H179" s="53">
+        <v>51730.8</v>
+      </c>
+    </row>
+    <row r="180" spans="2:8">
+      <c r="B180" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C180" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D180" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="E180" s="52">
+        <v>34661</v>
+      </c>
+      <c r="F180" s="53">
+        <v>2099</v>
+      </c>
+      <c r="G180" s="54">
+        <v>0</v>
+      </c>
+      <c r="H180" s="53">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="181" spans="2:8">
+      <c r="B181" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C181" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D181" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="E181" s="52">
+        <v>34662</v>
+      </c>
+      <c r="F181" s="53">
+        <v>45160.1</v>
+      </c>
+      <c r="G181" s="54">
+        <v>0</v>
+      </c>
+      <c r="H181" s="53">
+        <v>45160.1</v>
+      </c>
+    </row>
+    <row r="182" spans="2:8">
+      <c r="B182" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C182" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="E182" s="52">
+        <v>34664</v>
+      </c>
+      <c r="F182" s="53">
+        <v>4774.8500000000004</v>
+      </c>
+      <c r="G182" s="54">
+        <v>0</v>
+      </c>
+      <c r="H182" s="53">
+        <v>4774.8500000000004</v>
+      </c>
+    </row>
+    <row r="183" spans="2:8">
+      <c r="B183" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D183" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="E183" s="52">
+        <v>34677</v>
+      </c>
+      <c r="F183" s="53">
+        <v>64115.75</v>
+      </c>
+      <c r="G183" s="54">
+        <v>0</v>
+      </c>
+      <c r="H183" s="53">
+        <v>64115.75</v>
+      </c>
+    </row>
+    <row r="184" spans="2:8">
+      <c r="B184" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C184" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D184" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="E184" s="52">
+        <v>34678</v>
+      </c>
+      <c r="F184" s="53">
+        <v>2577.85</v>
+      </c>
+      <c r="G184" s="54">
+        <v>0</v>
+      </c>
+      <c r="H184" s="53">
+        <v>2577.85</v>
+      </c>
+    </row>
+    <row r="185" spans="2:8">
+      <c r="B185" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C185" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="E185" s="52">
+        <v>34679</v>
+      </c>
+      <c r="F185" s="53">
+        <v>1999</v>
+      </c>
+      <c r="G185" s="54">
+        <v>0</v>
+      </c>
+      <c r="H185" s="53">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="186" spans="2:8">
+      <c r="B186" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C186" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="E186" s="52">
+        <v>34682</v>
+      </c>
+      <c r="F186" s="53">
+        <v>158922.65</v>
+      </c>
+      <c r="G186" s="54">
+        <v>0</v>
+      </c>
+      <c r="H186" s="53">
+        <v>158922.65</v>
+      </c>
+    </row>
+    <row r="187" spans="2:8">
+      <c r="B187" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C187" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D187" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="E187" s="52">
+        <v>34683</v>
+      </c>
+      <c r="F187" s="53">
+        <v>6935</v>
+      </c>
+      <c r="G187" s="54">
+        <v>0</v>
+      </c>
+      <c r="H187" s="53">
+        <v>6935</v>
+      </c>
+    </row>
+    <row r="188" spans="2:8">
+      <c r="B188" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C188" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D188" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="E188" s="52">
+        <v>34684</v>
+      </c>
+      <c r="F188" s="53">
+        <v>1400</v>
+      </c>
+      <c r="G188" s="54">
+        <v>0</v>
+      </c>
+      <c r="H188" s="53">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="189" spans="2:8">
+      <c r="B189" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C189" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D189" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E189" s="52">
+        <v>34688</v>
+      </c>
+      <c r="F189" s="53">
+        <v>304</v>
+      </c>
+      <c r="G189" s="54">
+        <v>0</v>
+      </c>
+      <c r="H189" s="53">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="190" spans="2:8">
+      <c r="B190" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D190" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="E190" s="52">
+        <v>34690</v>
+      </c>
+      <c r="F190" s="53">
+        <v>16939.5</v>
+      </c>
+      <c r="G190" s="54">
+        <v>0</v>
+      </c>
+      <c r="H190" s="53">
+        <v>16939.5</v>
+      </c>
+    </row>
+    <row r="191" spans="2:8">
+      <c r="B191" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C191" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D191" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="E191" s="52">
+        <v>34691</v>
+      </c>
+      <c r="F191" s="53">
+        <v>11568</v>
+      </c>
+      <c r="G191" s="54">
+        <v>0</v>
+      </c>
+      <c r="H191" s="53">
+        <v>11568</v>
+      </c>
+    </row>
+    <row r="192" spans="2:8">
+      <c r="B192" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C192" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D192" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="E192" s="52">
+        <v>34694</v>
+      </c>
+      <c r="F192" s="53">
+        <v>4317.75</v>
+      </c>
+      <c r="G192" s="54">
+        <v>0</v>
+      </c>
+      <c r="H192" s="53">
+        <v>4317.75</v>
+      </c>
+    </row>
+    <row r="193" spans="2:8">
+      <c r="B193" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C193" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D193" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E193" s="52">
+        <v>34698</v>
+      </c>
+      <c r="F193" s="53">
+        <v>7134</v>
+      </c>
+      <c r="G193" s="54">
+        <v>0</v>
+      </c>
+      <c r="H193" s="53">
+        <v>7134</v>
+      </c>
+    </row>
+    <row r="194" spans="2:8">
+      <c r="B194" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="C194" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="E194" s="52">
+        <v>34700</v>
+      </c>
+      <c r="F194" s="53">
+        <v>7986.9</v>
+      </c>
+      <c r="G194" s="54">
+        <v>0</v>
+      </c>
+      <c r="H194" s="53">
+        <v>7986.9</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8">
+      <c r="B195" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C195" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D195" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="E195" s="52">
+        <v>34703</v>
+      </c>
+      <c r="F195" s="53">
+        <v>3304.85</v>
+      </c>
+      <c r="G195" s="54">
+        <v>0</v>
+      </c>
+      <c r="H195" s="53">
+        <v>3304.85</v>
+      </c>
+    </row>
+    <row r="196" spans="2:8">
+      <c r="B196" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C196" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D196" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="E196" s="52">
+        <v>34705</v>
+      </c>
+      <c r="F196" s="53">
+        <v>17917</v>
+      </c>
+      <c r="G196" s="54">
+        <v>0</v>
+      </c>
+      <c r="H196" s="53">
+        <v>17917</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8">
+      <c r="B197" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="C197" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D197" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="E197" s="52">
+        <v>34707</v>
+      </c>
+      <c r="F197" s="53">
+        <v>7423.35</v>
+      </c>
+      <c r="G197" s="54">
+        <v>0</v>
+      </c>
+      <c r="H197" s="53">
+        <v>7423.35</v>
+      </c>
+    </row>
+    <row r="198" spans="2:8">
+      <c r="B198" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C198" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E198" s="52">
+        <v>34708</v>
+      </c>
+      <c r="F198" s="53">
+        <v>9897</v>
+      </c>
+      <c r="G198" s="54">
+        <v>0</v>
+      </c>
+      <c r="H198" s="53">
+        <v>9897</v>
+      </c>
+    </row>
+    <row r="199" spans="2:8">
+      <c r="B199" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C199" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D199" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E199" s="52">
+        <v>34709</v>
+      </c>
+      <c r="F199" s="53">
+        <v>52729.25</v>
+      </c>
+      <c r="G199" s="54">
+        <v>0</v>
+      </c>
+      <c r="H199" s="53">
+        <v>52729.25</v>
+      </c>
+    </row>
+    <row r="200" spans="2:8">
+      <c r="B200" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C200" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D200" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="E200" s="52">
+        <v>34715</v>
+      </c>
+      <c r="F200" s="53">
+        <v>24485</v>
+      </c>
+      <c r="G200" s="54">
+        <v>0</v>
+      </c>
+      <c r="H200" s="53">
+        <v>24485</v>
+      </c>
+    </row>
+    <row r="201" spans="2:8">
+      <c r="B201" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C201" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="E201" s="52">
+        <v>34719</v>
+      </c>
+      <c r="F201" s="53">
+        <v>3065</v>
+      </c>
+      <c r="G201" s="54">
+        <v>0</v>
+      </c>
+      <c r="H201" s="53">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="202" spans="2:8">
+      <c r="B202" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C202" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="E202" s="52">
+        <v>34721</v>
+      </c>
+      <c r="F202" s="53">
+        <v>465</v>
+      </c>
+      <c r="G202" s="54">
+        <v>0</v>
+      </c>
+      <c r="H202" s="53">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8">
+      <c r="B203" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C203" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D203" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="E203" s="52">
+        <v>34725</v>
+      </c>
+      <c r="F203" s="53">
+        <v>5037.1000000000004</v>
+      </c>
+      <c r="G203" s="54">
+        <v>0</v>
+      </c>
+      <c r="H203" s="53">
+        <v>5037.1000000000004</v>
+      </c>
+    </row>
+    <row r="204" spans="2:8">
+      <c r="B204" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C204" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D204" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E204" s="52">
+        <v>34731</v>
+      </c>
+      <c r="F204" s="53">
+        <v>7572</v>
+      </c>
+      <c r="G204" s="54">
+        <v>0</v>
+      </c>
+      <c r="H204" s="53">
+        <v>7572</v>
+      </c>
+    </row>
+    <row r="205" spans="2:8">
+      <c r="B205" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C205" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D205" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="E205" s="52">
+        <v>34732</v>
+      </c>
+      <c r="F205" s="53">
+        <v>8939.6</v>
+      </c>
+      <c r="G205" s="54">
+        <v>0</v>
+      </c>
+      <c r="H205" s="53">
+        <v>8939.6</v>
+      </c>
+    </row>
+    <row r="206" spans="2:8">
+      <c r="B206" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C206" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D206" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="E206" s="52">
+        <v>34735</v>
+      </c>
+      <c r="F206" s="53">
+        <v>13908</v>
+      </c>
+      <c r="G206" s="54">
+        <v>0</v>
+      </c>
+      <c r="H206" s="53">
+        <v>13908</v>
+      </c>
+    </row>
+    <row r="207" spans="2:8">
+      <c r="B207" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C207" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D207" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="E207" s="52"/>
+      <c r="F207" s="53">
+        <v>65</v>
+      </c>
+      <c r="G207" s="54">
+        <v>0</v>
+      </c>
+      <c r="H207" s="53">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:conditionalFormatting sqref="C3:C3">
     <x:cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -2341,14 +2341,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr codeName="Лист3">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
   <x:dimension ref="A2:H207"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="5.164062" style="0" customWidth="1"/>
-    <x:col min="2" max="8" width="10.832031" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="5.164062" customWidth="1"/>
+    <x:col min="2" max="8" width="10.832031" customWidth="1"/>
   </x:cols>
   <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="2" spans="1:8" ht="30.75" customHeight="1">
@@ -7097,28 +7096,24 @@
       <x:formula>"VISA"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="9" fitToHeight="255" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
+  <x:pageSetup paperSize="9" fitToHeight="255" orientation="portrait" r:id="rId1"/>
   <x:headerFooter alignWithMargins="0"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="B3:H9"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.332031" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.5" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30.164062" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15.332031" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.5" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="4.332031" customWidth="1"/>
+    <x:col min="2" max="2" width="17.5" customWidth="1"/>
+    <x:col min="3" max="3" width="30.164062" customWidth="1"/>
+    <x:col min="4" max="4" width="15.332031" customWidth="1"/>
+    <x:col min="5" max="5" width="15.5" customWidth="1"/>
+    <x:col min="6" max="6" width="13.832031" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:8">
@@ -7259,27 +7254,21 @@
     <x:mergeCell ref="B9:D9"/>
   </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter alignWithMargins="0"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B1:E9"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.210625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.164062" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.5" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="9.210625"/>
+    <x:col min="2" max="2" width="17.164062" customWidth="1"/>
+    <x:col min="3" max="3" width="14.5" customWidth="1"/>
+    <x:col min="4" max="4" width="20.5" customWidth="1"/>
+    <x:col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="1:5">
@@ -7349,11 +7338,7 @@
     <x:mergeCell ref="B7:C7"/>
     <x:mergeCell ref="B8:C8"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -2339,17 +2339,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr codeName="Лист3">
-    <x:pageSetUpPr fitToPage="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A2:H207"/>
-  <x:sheetFormatPr defaultRowHeight="11.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="5.164062" customWidth="1"/>
-    <x:col min="2" max="8" width="10.832031" customWidth="1"/>
-  </x:cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Лист3">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H207"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
+  <cols>
+    <col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <col min="2" max="8" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="2" spans="1:8" ht="30.75" customHeight="1">
       <c r="B2" s="49" t="s">
         <v>1</v>
@@ -7090,30 +7090,30 @@
       </c>
     </row>
   </sheetData>
-  <x:phoneticPr fontId="0" type="noConversion"/>
-  <x:conditionalFormatting sqref="C3:C3">
-    <x:cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
-      <x:formula>"VISA"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="9" fitToHeight="255" orientation="portrait" r:id="rId1"/>
-  <x:headerFooter alignWithMargins="0"/>
-</x:worksheet>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"VISA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="255" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="B3:H9"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.332031" customWidth="1"/>
+    <x:col min="1" max="1" width="4.33203125" customWidth="1"/>
     <x:col min="2" max="2" width="17.5" customWidth="1"/>
-    <x:col min="3" max="3" width="30.164062" customWidth="1"/>
-    <x:col min="4" max="4" width="15.332031" customWidth="1"/>
+    <x:col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <x:col min="4" max="4" width="15.33203125" customWidth="1"/>
     <x:col min="5" max="5" width="15.5" customWidth="1"/>
-    <x:col min="6" max="6" width="13.832031" customWidth="1"/>
+    <x:col min="6" max="6" width="13.83203125" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:8">
@@ -7245,13 +7245,13 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells count="7">
+    <x:mergeCell ref="B9:D9"/>
+    <x:mergeCell ref="C7:D7"/>
     <x:mergeCell ref="E4:F4"/>
     <x:mergeCell ref="G4:G5"/>
     <x:mergeCell ref="H4:H5"/>
     <x:mergeCell ref="B6:B7"/>
-    <x:mergeCell ref="C7:D7"/>
     <x:mergeCell ref="B8:D8"/>
-    <x:mergeCell ref="B9:D9"/>
   </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7260,12 +7260,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:dimension ref="B1:E9"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.210625"/>
-    <x:col min="2" max="2" width="17.164062" customWidth="1"/>
+    <x:col min="2" max="2" width="17.1640625" customWidth="1"/>
     <x:col min="3" max="3" width="14.5" customWidth="1"/>
     <x:col min="4" max="4" width="20.5" customWidth="1"/>
     <x:col min="5" max="5" width="11" bestFit="1" customWidth="1"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -7115,135 +7115,135 @@
     <x:col min="5" max="5" width="15.5" customWidth="1"/>
     <x:col min="6" max="6" width="13.832031" customWidth="1"/>
   </x:cols>
-  <x:sheetData>
-    <x:row r="3" spans="1:8">
-      <x:c r="B3" s="4"/>
-      <x:c r="C3" s="6"/>
-      <x:c r="D3" s="6"/>
-      <x:c r="E3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="6"/>
-      <x:c r="H3" s="7"/>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="11.25" customHeight="1">
-      <x:c r="B4" s="9"/>
-      <x:c r="C4" s="8"/>
-      <x:c r="D4" s="8"/>
-      <x:c r="E4" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="6"/>
-      <x:c r="G4" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H4" s="40" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8" ht="25.5" customHeight="1">
-      <x:c r="B5" s="13" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="13" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F5" s="13" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="41"/>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="B6" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8" ht="12" customHeight="1">
-      <x:c r="B8" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="3"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8" ht="12.75" customHeight="1">
-      <x:c r="B9" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="3"/>
-      <x:c r="D9" s="3"/>
-      <x:c r="E9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="3" spans="2:8">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="2:8" ht="11.25" customHeight="1">
+      <c r="B4" s="9"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="25.5">
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="12">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="12.75">
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <x:mergeCells count="7">
     <x:mergeCell ref="E4:F4"/>
     <x:mergeCell ref="G4:G5"/>
@@ -7270,70 +7270,77 @@
     <x:col min="4" max="4" width="20.5" customWidth="1"/>
     <x:col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData>
-    <x:row r="4" spans="1:5">
-      <x:c r="B4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C4" s="6"/>
-      <x:c r="D4" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E4" s="7"/>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="B5" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="B6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5" ht="11.25" customHeight="1">
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11"/>
-      <x:c r="D7" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="B8" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="11"/>
-      <x:c r="D8" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="1" spans="2:5" s="1" customFormat="1"/>
+    <row r="4" spans="2:5">
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="11.25" customHeight="1">
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+  </sheetData>
   <x:mergeCells count="2">
     <x:mergeCell ref="B7:C7"/>
     <x:mergeCell ref="B8:C8"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -7103,242 +7103,249 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="B3:H9"/>
-  <x:sheetFormatPr defaultRowHeight="11.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <x:col min="2" max="2" width="17.5" customWidth="1"/>
-    <x:col min="3" max="3" width="30.1640625" customWidth="1"/>
-    <x:col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <x:col min="5" max="5" width="15.5" customWidth="1"/>
-    <x:col min="6" max="6" width="13.83203125" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="3" spans="1:8">
-      <x:c r="B3" s="4"/>
-      <x:c r="C3" s="6"/>
-      <x:c r="D3" s="6"/>
-      <x:c r="E3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="6"/>
-      <x:c r="H3" s="7"/>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="11.25" customHeight="1">
-      <x:c r="B4" s="9"/>
-      <x:c r="C4" s="8"/>
-      <x:c r="D4" s="8"/>
-      <x:c r="E4" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="6"/>
-      <x:c r="G4" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H4" s="40" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8" ht="25.5" customHeight="1">
-      <x:c r="B5" s="13" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="13" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F5" s="13" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="41"/>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="B6" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8" ht="12" customHeight="1">
-      <x:c r="B8" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="3"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8" ht="12.75" customHeight="1">
-      <x:c r="B9" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="3"/>
-      <x:c r="D9" s="3"/>
-      <x:c r="E9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B9:D9"/>
-    <x:mergeCell ref="C7:D7"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:G5"/>
-    <x:mergeCell ref="H4:H5"/>
-    <x:mergeCell ref="B6:B7"/>
-    <x:mergeCell ref="B8:D8"/>
-  </x:mergeCells>
-  <x:phoneticPr fontId="0" type="noConversion"/>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:headerFooter alignWithMargins="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B3:H9"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
+  <cols>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="2:8" ht="11.25" customHeight="1">
+      <c r="B4" s="9"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="25.5">
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="12">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="12.75">
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="B1:E9"/>
-  <x:sheetFormatPr defaultRowHeight="11.25"/>
-  <x:cols>
-    <x:col min="2" max="2" width="17.1640625" customWidth="1"/>
-    <x:col min="3" max="3" width="14.5" customWidth="1"/>
-    <x:col min="4" max="4" width="20.5" customWidth="1"/>
-    <x:col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="4" spans="1:5">
-      <x:c r="B4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C4" s="6"/>
-      <x:c r="D4" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E4" s="7"/>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="B5" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="B6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5" ht="11.25" customHeight="1">
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11"/>
-      <x:c r="D7" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="B8" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="11"/>
-      <x:c r="D8" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells count="2">
-    <x:mergeCell ref="B7:C7"/>
-    <x:mergeCell ref="B8:C8"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:E9"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
+  <cols>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" s="1" customFormat="1"/>
+    <row r="4" spans="2:5">
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="11.25" customHeight="1">
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
